--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -47729,6 +47729,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2060">
+      <c r="A2060" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2060" t="n">
+        <v>12500</v>
+      </c>
+      <c r="C2060" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G2060" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -47752,6 +47752,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2061">
+      <c r="A2061" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2061" t="n">
+        <v>27500</v>
+      </c>
+      <c r="C2061" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2061" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -47775,6 +47775,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2062" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C2062" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2062" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -47786,7 +47786,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="D2062" t="n">
-        <v>1.42999994754791</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="E2062" t="n">
         <v>1.42999994754791</v>
@@ -47795,6 +47795,29 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G2062" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2063" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C2063" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="G2063" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -47639,22 +47639,22 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2056" t="n">
-        <v>3000</v>
+        <v>19000</v>
       </c>
       <c r="C2056" t="n">
-        <v>1.51999998092651</v>
+        <v>1.55999994277954</v>
       </c>
       <c r="D2056" t="n">
-        <v>1.51999998092651</v>
+        <v>1.5</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.51999998092651</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.51999998092651</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="G2056" t="s">
         <v>7</v>
@@ -47662,22 +47662,22 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2057" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="C2057" t="n">
-        <v>1.48000001907349</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="D2057" t="n">
-        <v>1.48000001907349</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.48000001907349</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.48000001907349</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="G2057" t="s">
         <v>7</v>
@@ -47685,22 +47685,22 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2058" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="C2058" t="n">
-        <v>1.52999997138977</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="D2058" t="n">
-        <v>1.5</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.5</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.52999997138977</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="G2058" t="s">
         <v>7</v>
@@ -47708,22 +47708,22 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2059" t="n">
-        <v>13000</v>
+        <v>4500</v>
       </c>
       <c r="C2059" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D2059" t="n">
         <v>1.5</v>
       </c>
-      <c r="D2059" t="n">
-        <v>1.47000002861023</v>
-      </c>
       <c r="E2059" t="n">
-        <v>1.49000000953674</v>
+        <v>1.5</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.49000000953674</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="G2059" t="s">
         <v>7</v>
@@ -47731,22 +47731,22 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2060" t="n">
-        <v>12500</v>
+        <v>13000</v>
       </c>
       <c r="C2060" t="n">
         <v>1.5</v>
       </c>
       <c r="D2060" t="n">
-        <v>1.45000004768372</v>
+        <v>1.47000002861023</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.5</v>
+        <v>1.49000000953674</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.45000004768372</v>
+        <v>1.49000000953674</v>
       </c>
       <c r="G2060" t="s">
         <v>7</v>
@@ -47754,22 +47754,22 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2061" t="n">
-        <v>27500</v>
+        <v>12500</v>
       </c>
       <c r="C2061" t="n">
-        <v>1.47000002861023</v>
+        <v>1.5</v>
       </c>
       <c r="D2061" t="n">
-        <v>1.41999995708466</v>
+        <v>1.45000004768372</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.47000002861023</v>
+        <v>1.5</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.44000005722046</v>
+        <v>1.45000004768372</v>
       </c>
       <c r="G2061" t="s">
         <v>7</v>
@@ -47777,22 +47777,22 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2062" t="n">
-        <v>9500</v>
+        <v>27500</v>
       </c>
       <c r="C2062" t="n">
-        <v>1.45000004768372</v>
+        <v>1.47000002861023</v>
       </c>
       <c r="D2062" t="n">
-        <v>1.4099999666214</v>
+        <v>1.41999995708466</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.42999994754791</v>
+        <v>1.47000002861023</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.4099999666214</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="G2062" t="s">
         <v>7</v>
@@ -47800,24 +47800,47 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2063" t="n">
-        <v>11000</v>
+        <v>9500</v>
       </c>
       <c r="C2063" t="n">
-        <v>1.44000005722046</v>
+        <v>1.45000004768372</v>
       </c>
       <c r="D2063" t="n">
-        <v>1.37999999523163</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="E2063" t="n">
         <v>1.42999994754791</v>
       </c>
       <c r="F2063" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2063" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2064" t="n">
+        <v>12500</v>
+      </c>
+      <c r="C2064" t="n">
         <v>1.47000002861023</v>
       </c>
-      <c r="G2063" t="s">
+      <c r="D2064" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="G2064" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -54091,6 +54091,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H2067" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -54117,6 +54117,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2068" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05804991722107</v>
+        <v>3.05805015563965</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.4284999370575</v>
       </c>
       <c r="G4" t="n">
-        <v>3.08459115028381</v>
+        <v>3.08459091186523</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05850005149841</v>
+        <v>3.05849981307983</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05850005149841</v>
+        <v>3.05849981307983</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05445146560669</v>
+        <v>3.05445122718811</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0409562587738</v>
+        <v>3.04095602035522</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>3.0409562587738</v>
+        <v>3.04095602035522</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.21050000190735</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8884584903717</v>
+        <v>2.88845825195312</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.21749997138977</v>
       </c>
       <c r="G48" t="n">
-        <v>2.89475607872009</v>
+        <v>2.89475631713867</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>2.90510272979736</v>
+        <v>2.90510296821594</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.90510272979736</v>
+        <v>2.90510296821594</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G51" t="n">
-        <v>2.87856197357178</v>
+        <v>2.8785617351532</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G52" t="n">
-        <v>2.87856197357178</v>
+        <v>2.8785617351532</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G53" t="n">
-        <v>2.87856197357178</v>
+        <v>2.8785617351532</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.21449995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89205718040466</v>
+        <v>2.89205694198608</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.18350005149841</v>
       </c>
       <c r="G62" t="n">
-        <v>2.86416673660278</v>
+        <v>2.86416697502136</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.05100011825562</v>
       </c>
       <c r="G73" t="n">
-        <v>2.74495792388916</v>
+        <v>2.74495768547058</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.69007635116577</v>
+        <v>2.69007658958435</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>2.69007635116577</v>
+        <v>2.69007658958435</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.69007635116577</v>
+        <v>2.69007658958435</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G88" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G92" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G94" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.02649998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7229151725769</v>
+        <v>2.72291541099548</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.81949996948242</v>
       </c>
       <c r="G132" t="n">
-        <v>2.53667902946472</v>
+        <v>2.5366792678833</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>2.42016911506653</v>
+        <v>2.42016935348511</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>2.14126491546631</v>
+        <v>2.14126515388489</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.14126491546631</v>
+        <v>2.14126515388489</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G160" t="n">
-        <v>2.0863835811615</v>
+        <v>2.08638381958008</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G165" t="n">
-        <v>2.0863835811615</v>
+        <v>2.08638381958008</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.24023079872131</v>
+        <v>2.24023103713989</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.24023079872131</v>
+        <v>2.24023103713989</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35719084739685</v>
+        <v>2.35719060897827</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38418173789978</v>
+        <v>2.3841814994812</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G200" t="n">
-        <v>2.27621865272522</v>
+        <v>2.27621841430664</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G201" t="n">
-        <v>2.27621865272522</v>
+        <v>2.27621841430664</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.27621865272522</v>
+        <v>2.27621841430664</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G211" t="n">
-        <v>2.23123407363892</v>
+        <v>2.23123383522034</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G212" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.5</v>
       </c>
       <c r="G216" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.5</v>
       </c>
       <c r="G228" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.5</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.5</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.5</v>
       </c>
       <c r="G231" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>1.97032368183136</v>
+        <v>1.97032356262207</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>1.98831748962402</v>
+        <v>1.98831737041473</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G255" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G262" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G263" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>2.14126491546631</v>
+        <v>2.14126515388489</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G280" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G285" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G287" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G288" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G308" t="n">
-        <v>1.96132683753967</v>
+        <v>1.96132671833038</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G309" t="n">
-        <v>1.96132683753967</v>
+        <v>1.96132671833038</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.88035440444946</v>
+        <v>1.88035428524017</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G312" t="n">
-        <v>1.88035440444946</v>
+        <v>1.88035428524017</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G313" t="n">
-        <v>1.87135756015778</v>
+        <v>1.87135744094849</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G314" t="n">
-        <v>1.87135756015778</v>
+        <v>1.87135744094849</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G329" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87135756015778</v>
+        <v>1.87135744094849</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G346" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G349" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>1.7633945941925</v>
+        <v>1.76339471340179</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G414" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G417" t="n">
-        <v>1.50248408317566</v>
+        <v>1.50248420238495</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>1.7633945941925</v>
+        <v>1.76339471340179</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.78138852119446</v>
+        <v>1.78138840198517</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G427" t="n">
-        <v>1.8173760175705</v>
+        <v>1.81737613677979</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>1.75439786911011</v>
+        <v>1.75439774990082</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70941317081451</v>
+        <v>1.70941305160522</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G438" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G440" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G446" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G447" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G448" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G451" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G476" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G478" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G483" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G484" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G487" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G488" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G489" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G491" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G492" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G493" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G494" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G495" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G497" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G499" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G500" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G502" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G503" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G504" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G505" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G506" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G507" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G508" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G509" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G510" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G516" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G517" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G526" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G528" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G546" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>0.908688008785248</v>
+        <v>0.908688068389893</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G554" t="n">
-        <v>0.760239064693451</v>
+        <v>0.760239005088806</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G559" t="n">
-        <v>0.710756003856659</v>
+        <v>0.710756063461304</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G560" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G561" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G563" t="n">
-        <v>0.719752967357635</v>
+        <v>0.719752907752991</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G565" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G569" t="n">
-        <v>0.620786905288696</v>
+        <v>0.620786845684052</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G570" t="n">
-        <v>0.589297711849213</v>
+        <v>0.589297652244568</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>0.625</v>
       </c>
       <c r="G574" t="n">
-        <v>0.562307000160217</v>
+        <v>0.562306940555573</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G580" t="n">
-        <v>0.620786905288696</v>
+        <v>0.620786845684052</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G590" t="n">
-        <v>0.760239064693451</v>
+        <v>0.760239005088806</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G599" t="n">
-        <v>0.836712718009949</v>
+        <v>0.836712777614594</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G607" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G614" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G619" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G621" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G622" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>0.908688008785248</v>
+        <v>0.908688068389893</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>0.881697297096252</v>
+        <v>0.881697356700897</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>0.881697297096252</v>
+        <v>0.881697356700897</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G637" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.25</v>
       </c>
       <c r="G660" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G662" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G670" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.25</v>
       </c>
       <c r="G676" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G705" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G712" t="n">
-        <v>1.50248408317566</v>
+        <v>1.50248420238495</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G717" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G720" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G722" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G726" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G727" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G735" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G743" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G750" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G789" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G791" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G803" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G804" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G818" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G819" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G841" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G844" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G846" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G860" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G861" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G870" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G871" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G872" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G878" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G887" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G888" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G889" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.17859542369843</v>
+        <v>1.17859530448914</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G918" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G922" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G925" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G926" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G929" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G934" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G935" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G936" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>1.20108759403229</v>
+        <v>1.20108771324158</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>1.20108759403229</v>
+        <v>1.20108771324158</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G961" t="n">
-        <v>1.29105663299561</v>
+        <v>1.2910567522049</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G964" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G972" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G981" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G986" t="n">
-        <v>1.17409682273865</v>
+        <v>1.17409694194794</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G987" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G988" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G989" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G990" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G992" t="n">
-        <v>1.19209086894989</v>
+        <v>1.1920907497406</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G993" t="n">
-        <v>1.19209086894989</v>
+        <v>1.1920907497406</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>1.19209086894989</v>
+        <v>1.1920907497406</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G997" t="n">
-        <v>1.17859542369843</v>
+        <v>1.17859530448914</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G999" t="n">
-        <v>1.12011539936066</v>
+        <v>1.12011551856995</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.25</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.25</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.25</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.12011539936066</v>
+        <v>1.12011551856995</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.949174106121063</v>
+        <v>0.949174046516418</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.25</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.21008455753326</v>
+        <v>1.21008467674255</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.25</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -54140,6 +54140,32 @@
         <v>1.5</v>
       </c>
       <c r="H2068" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2069" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2069" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="H2069" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -47959,6 +47959,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2070">
+      <c r="A2070" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2070" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="G2070" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -54247,6 +54247,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2073" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C2073" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="H2073" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -48113,7 +48113,9 @@
       <c r="E2076" t="n">
         <v>1.41999995708466</v>
       </c>
-      <c r="F2076"/>
+      <c r="F2076" t="n">
+        <v>1.45000004768372</v>
+      </c>
       <c r="G2076" t="s">
         <v>7</v>
       </c>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -48120,6 +48120,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2077" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2077" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G2077" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2078"/>
+      <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -48159,8 +48159,31 @@
       <c r="E2078" t="n">
         <v>1.42999994754791</v>
       </c>
-      <c r="F2078"/>
+      <c r="F2078" t="n">
+        <v>1.42999994754791</v>
+      </c>
       <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2079"/>
+      <c r="G2079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -48182,8 +48182,31 @@
       <c r="E2079" t="n">
         <v>1.42999994754791</v>
       </c>
-      <c r="F2079"/>
+      <c r="F2079" t="n">
+        <v>1.39999997615814</v>
+      </c>
       <c r="G2079" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2080"/>
+      <c r="G2080" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -48212,6 +48212,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="G2081" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -54533,6 +54533,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="H2084" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -54559,6 +54559,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H2085" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -60843,6 +60843,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2086">
+      <c r="A2086" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2086" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>500</v>
+      </c>
+      <c r="I2086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2087" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I2087" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -60901,6 +60901,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2088">
+      <c r="A2088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2088" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2089" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I2089" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05805015563965</v>
+        <v>3.05804991722107</v>
       </c>
       <c r="H3" t="n">
         <v>192000</v>
@@ -485,7 +485,7 @@
         <v>3.4284999370575</v>
       </c>
       <c r="G4" t="n">
-        <v>3.08459091186523</v>
+        <v>3.08459115028381</v>
       </c>
       <c r="H4" t="n">
         <v>184000</v>
@@ -630,7 +630,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05849981307983</v>
+        <v>3.05850005149841</v>
       </c>
       <c r="H9" t="n">
         <v>8500</v>
@@ -688,7 +688,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05849981307983</v>
+        <v>3.05850005149841</v>
       </c>
       <c r="H11" t="n">
         <v>4000</v>
@@ -717,7 +717,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05445122718811</v>
+        <v>3.05445146560669</v>
       </c>
       <c r="H12" t="n">
         <v>9000</v>
@@ -775,7 +775,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04095602035522</v>
+        <v>3.0409562587738</v>
       </c>
       <c r="H14" t="n">
         <v>3000</v>
@@ -978,7 +978,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>3.04095602035522</v>
+        <v>3.0409562587738</v>
       </c>
       <c r="H21" t="n">
         <v>24500</v>
@@ -1268,7 +1268,7 @@
         <v>3.21050000190735</v>
       </c>
       <c r="G31" t="n">
-        <v>2.88845825195312</v>
+        <v>2.8884584903717</v>
       </c>
       <c r="H31" t="n">
         <v>16500</v>
@@ -1616,7 +1616,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H43" t="n">
         <v>3500</v>
@@ -1645,7 +1645,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>3.21749997138977</v>
       </c>
       <c r="G48" t="n">
-        <v>2.89475631713867</v>
+        <v>2.89475607872009</v>
       </c>
       <c r="H48" t="n">
         <v>11000</v>
@@ -1790,7 +1790,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>2.90510296821594</v>
+        <v>2.90510272979736</v>
       </c>
       <c r="H49" t="n">
         <v>3500</v>
@@ -1819,7 +1819,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.90510296821594</v>
+        <v>2.90510272979736</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G51" t="n">
-        <v>2.8785617351532</v>
+        <v>2.87856197357178</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8785617351532</v>
+        <v>2.87856197357178</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G53" t="n">
-        <v>2.8785617351532</v>
+        <v>2.87856197357178</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.21449995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89205694198608</v>
+        <v>2.89205718040466</v>
       </c>
       <c r="H54" t="n">
         <v>2500</v>
@@ -2138,7 +2138,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H61" t="n">
         <v>10000</v>
@@ -2167,7 +2167,7 @@
         <v>3.18350005149841</v>
       </c>
       <c r="G62" t="n">
-        <v>2.86416697502136</v>
+        <v>2.86416673660278</v>
       </c>
       <c r="H62" t="n">
         <v>8500</v>
@@ -2486,7 +2486,7 @@
         <v>3.05100011825562</v>
       </c>
       <c r="G73" t="n">
-        <v>2.74495768547058</v>
+        <v>2.74495792388916</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2660,7 +2660,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.69007658958435</v>
+        <v>2.69007635116577</v>
       </c>
       <c r="H79" t="n">
         <v>4500</v>
@@ -2689,7 +2689,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>2.69007658958435</v>
+        <v>2.69007635116577</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.69007658958435</v>
+        <v>2.69007635116577</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G88" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G92" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G94" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>3.02649998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72291541099548</v>
+        <v>2.7229151725769</v>
       </c>
       <c r="H109" t="n">
         <v>500</v>
@@ -4197,7 +4197,7 @@
         <v>2.81949996948242</v>
       </c>
       <c r="G132" t="n">
-        <v>2.5366792678833</v>
+        <v>2.53667902946472</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4284,7 +4284,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>2.42016935348511</v>
+        <v>2.42016911506653</v>
       </c>
       <c r="H135" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>2.14126515388489</v>
+        <v>2.14126491546631</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -4893,7 +4893,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.14126515388489</v>
+        <v>2.14126491546631</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G160" t="n">
-        <v>2.08638381958008</v>
+        <v>2.0863835811615</v>
       </c>
       <c r="H160" t="n">
         <v>2000</v>
@@ -5038,7 +5038,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5154,7 +5154,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G165" t="n">
-        <v>2.08638381958008</v>
+        <v>2.0863835811615</v>
       </c>
       <c r="H165" t="n">
         <v>1000</v>
@@ -5531,7 +5531,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H178" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H180" t="n">
         <v>3000</v>
@@ -5850,7 +5850,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.24023103713989</v>
+        <v>2.24023079872131</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.24023103713989</v>
+        <v>2.24023079872131</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35719060897827</v>
+        <v>2.35719084739685</v>
       </c>
       <c r="H193" t="n">
         <v>9500</v>
@@ -5995,7 +5995,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>2.3841814994812</v>
+        <v>2.38418173789978</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6169,7 +6169,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G200" t="n">
-        <v>2.27621841430664</v>
+        <v>2.27621865272522</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G201" t="n">
-        <v>2.27621841430664</v>
+        <v>2.27621865272522</v>
       </c>
       <c r="H201" t="n">
         <v>2500</v>
@@ -6227,7 +6227,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H202" t="n">
         <v>500</v>
@@ -6343,7 +6343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.27621841430664</v>
+        <v>2.27621865272522</v>
       </c>
       <c r="H206" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H207" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G211" t="n">
-        <v>2.23123383522034</v>
+        <v>2.23123407363892</v>
       </c>
       <c r="H211" t="n">
         <v>3500</v>
@@ -6517,7 +6517,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G212" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6546,7 +6546,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H213" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>2.5</v>
       </c>
       <c r="G216" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H218" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H219" t="n">
         <v>2500</v>
@@ -6778,7 +6778,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H221" t="n">
         <v>4500</v>
@@ -6807,7 +6807,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H222" t="n">
         <v>500</v>
@@ -6836,7 +6836,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -6981,7 +6981,7 @@
         <v>2.5</v>
       </c>
       <c r="G228" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>2.5</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H229" t="n">
         <v>500</v>
@@ -7039,7 +7039,7 @@
         <v>2.5</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.5</v>
       </c>
       <c r="G231" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7184,7 +7184,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H235" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>1.97032356262207</v>
+        <v>1.97032368183136</v>
       </c>
       <c r="H241" t="n">
         <v>14000</v>
@@ -7474,7 +7474,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H245" t="n">
         <v>2500</v>
@@ -7503,7 +7503,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7590,7 +7590,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H249" t="n">
         <v>3500</v>
@@ -7619,7 +7619,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H250" t="n">
         <v>1500</v>
@@ -7648,7 +7648,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H251" t="n">
         <v>2500</v>
@@ -7677,7 +7677,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H252" t="n">
         <v>1500</v>
@@ -7706,7 +7706,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>1.98831737041473</v>
+        <v>1.98831748962402</v>
       </c>
       <c r="H253" t="n">
         <v>1500</v>
@@ -7764,7 +7764,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G255" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H255" t="n">
         <v>8500</v>
@@ -7793,7 +7793,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H259" t="n">
         <v>1000</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H260" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H261" t="n">
         <v>500</v>
@@ -7967,7 +7967,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G262" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G263" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H264" t="n">
         <v>2500</v>
@@ -8257,7 +8257,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>2.14126515388489</v>
+        <v>2.14126491546631</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H274" t="n">
         <v>1000</v>
@@ -8344,7 +8344,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G280" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G285" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G287" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G288" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H290" t="n">
         <v>500</v>
@@ -8924,7 +8924,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H295" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H299" t="n">
         <v>1000</v>
@@ -9243,7 +9243,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H306" t="n">
         <v>2000</v>
@@ -9272,7 +9272,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G308" t="n">
-        <v>1.96132671833038</v>
+        <v>1.96132683753967</v>
       </c>
       <c r="H308" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G309" t="n">
-        <v>1.96132671833038</v>
+        <v>1.96132683753967</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.88035428524017</v>
+        <v>1.88035440444946</v>
       </c>
       <c r="H310" t="n">
         <v>13500</v>
@@ -9388,7 +9388,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H311" t="n">
         <v>25500</v>
@@ -9417,7 +9417,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G312" t="n">
-        <v>1.88035428524017</v>
+        <v>1.88035440444946</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G313" t="n">
-        <v>1.87135744094849</v>
+        <v>1.87135756015778</v>
       </c>
       <c r="H313" t="n">
         <v>58000</v>
@@ -9475,7 +9475,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G314" t="n">
-        <v>1.87135744094849</v>
+        <v>1.87135756015778</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9678,7 +9678,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H321" t="n">
         <v>1500</v>
@@ -9707,7 +9707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H322" t="n">
         <v>500</v>
@@ -9910,7 +9910,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G329" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H329" t="n">
         <v>500</v>
@@ -9939,7 +9939,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87135744094849</v>
+        <v>1.87135756015778</v>
       </c>
       <c r="H330" t="n">
         <v>2000</v>
@@ -9968,7 +9968,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H331" t="n">
         <v>3000</v>
@@ -9997,7 +9997,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H333" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H336" t="n">
         <v>5000</v>
@@ -10142,7 +10142,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H337" t="n">
         <v>8500</v>
@@ -10374,7 +10374,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H345" t="n">
         <v>2500</v>
@@ -10403,7 +10403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G346" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H347" t="n">
         <v>2500</v>
@@ -10461,7 +10461,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H348" t="n">
         <v>1000</v>
@@ -10490,7 +10490,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G349" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H356" t="n">
         <v>3000</v>
@@ -11650,7 +11650,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H389" t="n">
         <v>1000</v>
@@ -11679,7 +11679,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>1.76339471340179</v>
+        <v>1.7633945941925</v>
       </c>
       <c r="H397" t="n">
         <v>18000</v>
@@ -12143,7 +12143,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H406" t="n">
         <v>3500</v>
@@ -12375,7 +12375,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G414" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H414" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G417" t="n">
-        <v>1.50248420238495</v>
+        <v>1.50248408317566</v>
       </c>
       <c r="H417" t="n">
         <v>1500</v>
@@ -12665,7 +12665,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>1.76339471340179</v>
+        <v>1.7633945941925</v>
       </c>
       <c r="H424" t="n">
         <v>5500</v>
@@ -12723,7 +12723,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.78138840198517</v>
+        <v>1.78138852119446</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12752,7 +12752,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G427" t="n">
-        <v>1.81737613677979</v>
+        <v>1.8173760175705</v>
       </c>
       <c r="H427" t="n">
         <v>5500</v>
@@ -12810,7 +12810,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>1.75439774990082</v>
+        <v>1.75439786911011</v>
       </c>
       <c r="H429" t="n">
         <v>1000</v>
@@ -12897,7 +12897,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70941305160522</v>
+        <v>1.70941317081451</v>
       </c>
       <c r="H432" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G438" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H438" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G440" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H440" t="n">
         <v>25000</v>
@@ -13158,7 +13158,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H441" t="n">
         <v>21000</v>
@@ -13303,7 +13303,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G446" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H446" t="n">
         <v>16500</v>
@@ -13332,7 +13332,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G447" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H447" t="n">
         <v>11000</v>
@@ -13361,7 +13361,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G448" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H448" t="n">
         <v>11500</v>
@@ -13390,7 +13390,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H449" t="n">
         <v>9000</v>
@@ -13448,7 +13448,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G451" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H451" t="n">
         <v>25500</v>
@@ -13564,7 +13564,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H455" t="n">
         <v>14500</v>
@@ -13883,7 +13883,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H466" t="n">
         <v>8000</v>
@@ -13970,7 +13970,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H469" t="n">
         <v>25500</v>
@@ -13999,7 +13999,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H470" t="n">
         <v>4000</v>
@@ -14028,7 +14028,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H471" t="n">
         <v>6000</v>
@@ -14086,7 +14086,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H473" t="n">
         <v>5500</v>
@@ -14115,7 +14115,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H474" t="n">
         <v>17500</v>
@@ -14144,7 +14144,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H475" t="n">
         <v>23000</v>
@@ -14173,7 +14173,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G476" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H476" t="n">
         <v>8000</v>
@@ -14231,7 +14231,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G478" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H478" t="n">
         <v>5000</v>
@@ -14376,7 +14376,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G483" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H483" t="n">
         <v>13500</v>
@@ -14405,7 +14405,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G484" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H484" t="n">
         <v>5000</v>
@@ -14492,7 +14492,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G487" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H487" t="n">
         <v>4500</v>
@@ -14521,7 +14521,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G488" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14550,7 +14550,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G489" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G491" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H491" t="n">
         <v>1000</v>
@@ -14637,7 +14637,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G492" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G493" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G494" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H494" t="n">
         <v>1500</v>
@@ -14724,7 +14724,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G495" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H495" t="n">
         <v>1500</v>
@@ -14753,7 +14753,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H496" t="n">
         <v>1500</v>
@@ -14782,7 +14782,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G497" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H497" t="n">
         <v>2500</v>
@@ -14811,7 +14811,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H498" t="n">
         <v>2500</v>
@@ -14840,7 +14840,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G499" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H499" t="n">
         <v>2500</v>
@@ -14869,7 +14869,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G500" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G502" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H502" t="n">
         <v>12500</v>
@@ -14956,7 +14956,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G503" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -14985,7 +14985,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G504" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H504" t="n">
         <v>6000</v>
@@ -15014,7 +15014,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G505" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H505" t="n">
         <v>6000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G506" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G507" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H507" t="n">
         <v>1000</v>
@@ -15101,7 +15101,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G508" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G509" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G510" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G516" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H516" t="n">
         <v>12000</v>
@@ -15362,7 +15362,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G517" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H523" t="n">
         <v>13000</v>
@@ -15594,7 +15594,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H525" t="n">
         <v>7500</v>
@@ -15623,7 +15623,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G526" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H526" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G528" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H529" t="n">
         <v>26500</v>
@@ -15855,7 +15855,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H534" t="n">
         <v>41500</v>
@@ -15884,7 +15884,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H535" t="n">
         <v>5500</v>
@@ -15942,7 +15942,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H537" t="n">
         <v>2500</v>
@@ -16087,7 +16087,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H544" t="n">
         <v>500</v>
@@ -16174,7 +16174,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G546" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>0.908688068389893</v>
+        <v>0.908688008785248</v>
       </c>
       <c r="H548" t="n">
         <v>6500</v>
@@ -16435,7 +16435,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G554" t="n">
-        <v>0.760239005088806</v>
+        <v>0.760239064693451</v>
       </c>
       <c r="H554" t="n">
         <v>59000</v>
@@ -16580,7 +16580,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G559" t="n">
-        <v>0.710756063461304</v>
+        <v>0.710756003856659</v>
       </c>
       <c r="H559" t="n">
         <v>6500</v>
@@ -16609,7 +16609,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G560" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H560" t="n">
         <v>11500</v>
@@ -16638,7 +16638,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G561" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G563" t="n">
-        <v>0.719752907752991</v>
+        <v>0.719752967357635</v>
       </c>
       <c r="H563" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G565" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H565" t="n">
         <v>5500</v>
@@ -16783,7 +16783,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G569" t="n">
-        <v>0.620786845684052</v>
+        <v>0.620786905288696</v>
       </c>
       <c r="H569" t="n">
         <v>62000</v>
@@ -16899,7 +16899,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G570" t="n">
-        <v>0.589297652244568</v>
+        <v>0.589297711849213</v>
       </c>
       <c r="H570" t="n">
         <v>10000</v>
@@ -17015,7 +17015,7 @@
         <v>0.625</v>
       </c>
       <c r="G574" t="n">
-        <v>0.562306940555573</v>
+        <v>0.562307000160217</v>
       </c>
       <c r="H574" t="n">
         <v>27500</v>
@@ -17189,7 +17189,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G580" t="n">
-        <v>0.620786845684052</v>
+        <v>0.620786905288696</v>
       </c>
       <c r="H580" t="n">
         <v>149500</v>
@@ -17334,7 +17334,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H585" t="n">
         <v>427500</v>
@@ -17479,7 +17479,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G590" t="n">
-        <v>0.760239005088806</v>
+        <v>0.760239064693451</v>
       </c>
       <c r="H590" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G599" t="n">
-        <v>0.836712777614594</v>
+        <v>0.836712718009949</v>
       </c>
       <c r="H599" t="n">
         <v>16000</v>
@@ -17914,7 +17914,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H605" t="n">
         <v>35500</v>
@@ -17943,7 +17943,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H606" t="n">
         <v>4000</v>
@@ -17972,7 +17972,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G607" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G614" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H614" t="n">
         <v>210000</v>
@@ -18320,7 +18320,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G619" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H619" t="n">
         <v>26500</v>
@@ -18378,7 +18378,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G621" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G622" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H622" t="n">
         <v>20500</v>
@@ -18465,7 +18465,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H624" t="n">
         <v>40500</v>
@@ -18494,7 +18494,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H625" t="n">
         <v>3000</v>
@@ -18552,7 +18552,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>0.908688068389893</v>
+        <v>0.908688008785248</v>
       </c>
       <c r="H627" t="n">
         <v>28000</v>
@@ -18581,7 +18581,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H628" t="n">
         <v>11500</v>
@@ -18610,7 +18610,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>0.881697356700897</v>
+        <v>0.881697297096252</v>
       </c>
       <c r="H629" t="n">
         <v>5000</v>
@@ -18639,7 +18639,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>0.881697356700897</v>
+        <v>0.881697297096252</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18697,7 +18697,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H632" t="n">
         <v>23000</v>
@@ -18726,7 +18726,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H633" t="n">
         <v>17000</v>
@@ -18755,7 +18755,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H634" t="n">
         <v>4000</v>
@@ -18784,7 +18784,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H635" t="n">
         <v>3000</v>
@@ -18813,7 +18813,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H636" t="n">
         <v>17500</v>
@@ -18842,7 +18842,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G637" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H637" t="n">
         <v>43000</v>
@@ -19451,7 +19451,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H658" t="n">
         <v>2500</v>
@@ -19509,7 +19509,7 @@
         <v>1.25</v>
       </c>
       <c r="G660" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H660" t="n">
         <v>12500</v>
@@ -19567,7 +19567,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G662" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19596,7 +19596,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H663" t="n">
         <v>5500</v>
@@ -19625,7 +19625,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H665" t="n">
         <v>27000</v>
@@ -19799,7 +19799,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G670" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19886,7 +19886,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H673" t="n">
         <v>30500</v>
@@ -19944,7 +19944,7 @@
         <v>1.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H675" t="n">
         <v>10500</v>
@@ -19973,7 +19973,7 @@
         <v>1.25</v>
       </c>
       <c r="G676" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H676" t="n">
         <v>7000</v>
@@ -20147,7 +20147,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H682" t="n">
         <v>12000</v>
@@ -20234,7 +20234,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H685" t="n">
         <v>1000</v>
@@ -20263,7 +20263,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H686" t="n">
         <v>4000</v>
@@ -20553,7 +20553,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H696" t="n">
         <v>31000</v>
@@ -20814,7 +20814,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G705" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H705" t="n">
         <v>39500</v>
@@ -20988,7 +20988,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H711" t="n">
         <v>9500</v>
@@ -21017,7 +21017,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G712" t="n">
-        <v>1.50248420238495</v>
+        <v>1.50248408317566</v>
       </c>
       <c r="H712" t="n">
         <v>18500</v>
@@ -21162,7 +21162,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G717" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H717" t="n">
         <v>3000</v>
@@ -21249,7 +21249,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G720" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H720" t="n">
         <v>25500</v>
@@ -21307,7 +21307,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G722" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H722" t="n">
         <v>13500</v>
@@ -21336,7 +21336,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H723" t="n">
         <v>8000</v>
@@ -21423,7 +21423,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G726" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H726" t="n">
         <v>1000</v>
@@ -21452,7 +21452,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G727" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H727" t="n">
         <v>16000</v>
@@ -21481,7 +21481,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H730" t="n">
         <v>3500</v>
@@ -21684,7 +21684,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G735" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H735" t="n">
         <v>14000</v>
@@ -21916,7 +21916,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G743" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H743" t="n">
         <v>14500</v>
@@ -22119,7 +22119,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G750" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H750" t="n">
         <v>32500</v>
@@ -23250,7 +23250,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G789" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H789" t="n">
         <v>32000</v>
@@ -23308,7 +23308,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G791" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H791" t="n">
         <v>1000</v>
@@ -23656,7 +23656,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G803" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H803" t="n">
         <v>18500</v>
@@ -23685,7 +23685,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G804" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H804" t="n">
         <v>5000</v>
@@ -24091,7 +24091,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G818" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H818" t="n">
         <v>10000</v>
@@ -24120,7 +24120,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G819" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H819" t="n">
         <v>6000</v>
@@ -24410,7 +24410,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H829" t="n">
         <v>3000</v>
@@ -24439,7 +24439,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H830" t="n">
         <v>2000</v>
@@ -24584,7 +24584,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -24758,7 +24758,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G841" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H841" t="n">
         <v>14500</v>
@@ -24845,7 +24845,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G844" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H844" t="n">
         <v>17500</v>
@@ -24903,7 +24903,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G846" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H846" t="n">
         <v>18500</v>
@@ -25077,7 +25077,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H852" t="n">
         <v>12500</v>
@@ -25309,7 +25309,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G860" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H860" t="n">
         <v>3500</v>
@@ -25338,7 +25338,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G861" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H861" t="n">
         <v>3000</v>
@@ -25367,7 +25367,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G870" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H870" t="n">
         <v>2500</v>
@@ -25628,7 +25628,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G871" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H871" t="n">
         <v>6500</v>
@@ -25657,7 +25657,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G872" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H872" t="n">
         <v>8000</v>
@@ -25744,7 +25744,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H875" t="n">
         <v>500</v>
@@ -25773,7 +25773,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H876" t="n">
         <v>7500</v>
@@ -25802,7 +25802,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H877" t="n">
         <v>1000</v>
@@ -25831,7 +25831,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G878" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26092,7 +26092,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G887" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H887" t="n">
         <v>1000</v>
@@ -26121,7 +26121,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G888" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G889" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H889" t="n">
         <v>1500</v>
@@ -26759,7 +26759,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.17859530448914</v>
+        <v>1.17859542369843</v>
       </c>
       <c r="H910" t="n">
         <v>8000</v>
@@ -26904,7 +26904,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -26991,7 +26991,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G918" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H918" t="n">
         <v>9500</v>
@@ -27049,7 +27049,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27107,7 +27107,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G922" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H922" t="n">
         <v>500</v>
@@ -27136,7 +27136,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H923" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G925" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H925" t="n">
         <v>3500</v>
@@ -27223,7 +27223,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G926" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G929" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H929" t="n">
         <v>22000</v>
@@ -27455,7 +27455,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G934" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H934" t="n">
         <v>8000</v>
@@ -27484,7 +27484,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G935" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H935" t="n">
         <v>5500</v>
@@ -27513,7 +27513,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G936" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>1.20108771324158</v>
+        <v>1.20108759403229</v>
       </c>
       <c r="H938" t="n">
         <v>3500</v>
@@ -27600,7 +27600,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>1.20108771324158</v>
+        <v>1.20108759403229</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G961" t="n">
-        <v>1.2910567522049</v>
+        <v>1.29105663299561</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28325,7 +28325,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G964" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H964" t="n">
         <v>5000</v>
@@ -28557,7 +28557,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G972" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H972" t="n">
         <v>3500</v>
@@ -28644,7 +28644,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H975" t="n">
         <v>1000</v>
@@ -28673,7 +28673,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H976" t="n">
         <v>2000</v>
@@ -28702,7 +28702,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H978" t="n">
         <v>1000</v>
@@ -28818,7 +28818,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G981" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H981" t="n">
         <v>2500</v>
@@ -28963,7 +28963,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G986" t="n">
-        <v>1.17409694194794</v>
+        <v>1.17409682273865</v>
       </c>
       <c r="H986" t="n">
         <v>6500</v>
@@ -28992,7 +28992,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G987" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H987" t="n">
         <v>500</v>
@@ -29021,7 +29021,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G988" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -29050,7 +29050,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G989" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G990" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G992" t="n">
-        <v>1.1920907497406</v>
+        <v>1.19209086894989</v>
       </c>
       <c r="H992" t="n">
         <v>1000</v>
@@ -29166,7 +29166,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G993" t="n">
-        <v>1.1920907497406</v>
+        <v>1.19209086894989</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>1.1920907497406</v>
+        <v>1.19209086894989</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G997" t="n">
-        <v>1.17859530448914</v>
+        <v>1.17859542369843</v>
       </c>
       <c r="H997" t="n">
         <v>500</v>
@@ -29340,7 +29340,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G999" t="n">
-        <v>1.12011551856995</v>
+        <v>1.12011539936066</v>
       </c>
       <c r="H999" t="n">
         <v>4500</v>
@@ -29514,7 +29514,7 @@
         <v>1.25</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1005" t="n">
         <v>1500</v>
@@ -29543,7 +29543,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1006" t="n">
         <v>9000</v>
@@ -29601,7 +29601,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29630,7 +29630,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1009" t="n">
         <v>9500</v>
@@ -29659,7 +29659,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1011" t="n">
         <v>2500</v>
@@ -29717,7 +29717,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -29775,7 +29775,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>1.25</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1022" t="n">
         <v>4000</v>
@@ -30036,7 +30036,7 @@
         <v>1.25</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1023" t="n">
         <v>1500</v>
@@ -30065,7 +30065,7 @@
         <v>1.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1031" t="n">
         <v>11500</v>
@@ -30297,7 +30297,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -30326,7 +30326,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H1033" t="n">
         <v>3000</v>
@@ -30384,7 +30384,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.12011551856995</v>
+        <v>1.12011539936066</v>
       </c>
       <c r="H1035" t="n">
         <v>500</v>
@@ -30442,7 +30442,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H1037" t="n">
         <v>3000</v>
@@ -30558,7 +30558,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1041" t="n">
         <v>7500</v>
@@ -30674,7 +30674,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1045" t="n">
         <v>1000</v>
@@ -30703,7 +30703,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1052" t="n">
         <v>2000</v>
@@ -30993,7 +30993,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H1056" t="n">
         <v>6000</v>
@@ -31080,7 +31080,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1059" t="n">
         <v>500</v>
@@ -31109,7 +31109,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1060" t="n">
         <v>2500</v>
@@ -31138,7 +31138,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31167,7 +31167,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31196,7 +31196,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1064" t="n">
         <v>4000</v>
@@ -31254,7 +31254,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -31283,7 +31283,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1066" t="n">
         <v>500</v>
@@ -31312,7 +31312,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -31341,7 +31341,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -31399,7 +31399,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.949174046516418</v>
+        <v>0.949174106121063</v>
       </c>
       <c r="H1070" t="n">
         <v>7500</v>
@@ -31457,7 +31457,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1072" t="n">
         <v>4000</v>
@@ -31486,7 +31486,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H1073" t="n">
         <v>500</v>
@@ -31544,7 +31544,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1075" t="n">
         <v>1500</v>
@@ -31573,7 +31573,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1076" t="n">
         <v>500</v>
@@ -31602,7 +31602,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1077" t="n">
         <v>13500</v>
@@ -31776,7 +31776,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1083" t="n">
         <v>1000</v>
@@ -31805,7 +31805,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31834,7 +31834,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1085" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1086" t="n">
         <v>0</v>
@@ -31892,7 +31892,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1087" t="n">
         <v>0</v>
@@ -31921,7 +31921,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1088" t="n">
         <v>3500</v>
@@ -32008,7 +32008,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1091" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>1.25</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1092" t="n">
         <v>1000</v>
@@ -32791,7 +32791,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H1118" t="n">
         <v>2000</v>
@@ -32936,7 +32936,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1123" t="n">
         <v>6500</v>
@@ -32965,7 +32965,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1124" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H1136" t="n">
         <v>2500</v>
@@ -33342,7 +33342,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1137" t="n">
         <v>2500</v>
@@ -33371,7 +33371,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1138" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1139" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1140" t="n">
         <v>0</v>
@@ -33487,7 +33487,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1143" t="n">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H1145" t="n">
         <v>8000</v>
@@ -33719,7 +33719,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H1150" t="n">
         <v>8000</v>
@@ -33777,7 +33777,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H1152" t="n">
         <v>19500</v>
@@ -33835,7 +33835,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.21008467674255</v>
+        <v>1.21008455753326</v>
       </c>
       <c r="H1154" t="n">
         <v>6500</v>
@@ -33864,7 +33864,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H1155" t="n">
         <v>10500</v>
@@ -34067,7 +34067,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1162" t="n">
         <v>23000</v>
@@ -34096,7 +34096,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1163" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1164" t="n">
         <v>2500</v>
@@ -34183,7 +34183,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H1166" t="n">
         <v>17000</v>
@@ -34386,7 +34386,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H1173" t="n">
         <v>5500</v>
@@ -34415,7 +34415,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1174" t="n">
         <v>5500</v>
@@ -34444,7 +34444,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1176" t="n">
         <v>500</v>
@@ -34589,7 +34589,7 @@
         <v>1.25</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1180" t="n">
         <v>19500</v>
@@ -34647,7 +34647,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1182" t="n">
         <v>10000</v>
@@ -34676,7 +34676,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1183" t="n">
         <v>45500</v>
@@ -34763,7 +34763,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H1186" t="n">
         <v>52000</v>
@@ -34821,7 +34821,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H1188" t="n">
         <v>1000</v>
@@ -34850,7 +34850,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1189" t="n">
         <v>53000</v>
@@ -35024,7 +35024,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H1195" t="n">
         <v>5000</v>
@@ -35053,7 +35053,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1197" t="n">
         <v>76000</v>
@@ -35111,7 +35111,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H1198" t="n">
         <v>85500</v>
@@ -35256,7 +35256,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1203" t="n">
         <v>8500</v>
@@ -35285,7 +35285,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1204" t="n">
         <v>0</v>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -60988,6 +60988,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2091">
+      <c r="A2091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2091" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2092" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2092" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -61046,6 +61046,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2093">
+      <c r="A2093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2093" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05805015563965</v>
+        <v>3.05804991722107</v>
       </c>
       <c r="H3" t="n">
         <v>192000</v>
@@ -485,7 +485,7 @@
         <v>3.4284999370575</v>
       </c>
       <c r="G4" t="n">
-        <v>3.08459091186523</v>
+        <v>3.08459115028381</v>
       </c>
       <c r="H4" t="n">
         <v>184000</v>
@@ -630,7 +630,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05849981307983</v>
+        <v>3.05850005149841</v>
       </c>
       <c r="H9" t="n">
         <v>8500</v>
@@ -688,7 +688,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05849981307983</v>
+        <v>3.05850005149841</v>
       </c>
       <c r="H11" t="n">
         <v>4000</v>
@@ -717,7 +717,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05445122718811</v>
+        <v>3.05445146560669</v>
       </c>
       <c r="H12" t="n">
         <v>9000</v>
@@ -775,7 +775,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04095602035522</v>
+        <v>3.0409562587738</v>
       </c>
       <c r="H14" t="n">
         <v>3000</v>
@@ -978,7 +978,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>3.04095602035522</v>
+        <v>3.0409562587738</v>
       </c>
       <c r="H21" t="n">
         <v>24500</v>
@@ -1268,7 +1268,7 @@
         <v>3.21050000190735</v>
       </c>
       <c r="G31" t="n">
-        <v>2.88845825195312</v>
+        <v>2.8884584903717</v>
       </c>
       <c r="H31" t="n">
         <v>16500</v>
@@ -1616,7 +1616,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H43" t="n">
         <v>3500</v>
@@ -1645,7 +1645,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>3.21749997138977</v>
       </c>
       <c r="G48" t="n">
-        <v>2.89475631713867</v>
+        <v>2.89475607872009</v>
       </c>
       <c r="H48" t="n">
         <v>11000</v>
@@ -1790,7 +1790,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>2.90510296821594</v>
+        <v>2.90510272979736</v>
       </c>
       <c r="H49" t="n">
         <v>3500</v>
@@ -1819,7 +1819,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.90510296821594</v>
+        <v>2.90510272979736</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G51" t="n">
-        <v>2.8785617351532</v>
+        <v>2.87856197357178</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8785617351532</v>
+        <v>2.87856197357178</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G53" t="n">
-        <v>2.8785617351532</v>
+        <v>2.87856197357178</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.21449995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89205694198608</v>
+        <v>2.89205718040466</v>
       </c>
       <c r="H54" t="n">
         <v>2500</v>
@@ -2138,7 +2138,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.87901163101196</v>
+        <v>2.87901186943054</v>
       </c>
       <c r="H61" t="n">
         <v>10000</v>
@@ -2167,7 +2167,7 @@
         <v>3.18350005149841</v>
       </c>
       <c r="G62" t="n">
-        <v>2.86416697502136</v>
+        <v>2.86416673660278</v>
       </c>
       <c r="H62" t="n">
         <v>8500</v>
@@ -2486,7 +2486,7 @@
         <v>3.05100011825562</v>
       </c>
       <c r="G73" t="n">
-        <v>2.74495768547058</v>
+        <v>2.74495792388916</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2660,7 +2660,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.69007658958435</v>
+        <v>2.69007635116577</v>
       </c>
       <c r="H79" t="n">
         <v>4500</v>
@@ -2689,7 +2689,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>2.69007658958435</v>
+        <v>2.69007635116577</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.69007658958435</v>
+        <v>2.69007635116577</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G88" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G92" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G94" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>2.78769302368164</v>
+        <v>2.78769278526306</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>3.02649998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72291541099548</v>
+        <v>2.7229151725769</v>
       </c>
       <c r="H109" t="n">
         <v>500</v>
@@ -4197,7 +4197,7 @@
         <v>2.81949996948242</v>
       </c>
       <c r="G132" t="n">
-        <v>2.5366792678833</v>
+        <v>2.53667902946472</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4284,7 +4284,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>2.42016935348511</v>
+        <v>2.42016911506653</v>
       </c>
       <c r="H135" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>2.14126515388489</v>
+        <v>2.14126491546631</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -4893,7 +4893,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.14126515388489</v>
+        <v>2.14126491546631</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G160" t="n">
-        <v>2.08638381958008</v>
+        <v>2.0863835811615</v>
       </c>
       <c r="H160" t="n">
         <v>2000</v>
@@ -5038,7 +5038,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5154,7 +5154,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G165" t="n">
-        <v>2.08638381958008</v>
+        <v>2.0863835811615</v>
       </c>
       <c r="H165" t="n">
         <v>1000</v>
@@ -5531,7 +5531,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H178" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H180" t="n">
         <v>3000</v>
@@ -5850,7 +5850,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.24023103713989</v>
+        <v>2.24023079872131</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.24023103713989</v>
+        <v>2.24023079872131</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35719060897827</v>
+        <v>2.35719084739685</v>
       </c>
       <c r="H193" t="n">
         <v>9500</v>
@@ -5995,7 +5995,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>2.3841814994812</v>
+        <v>2.38418173789978</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6169,7 +6169,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G200" t="n">
-        <v>2.27621841430664</v>
+        <v>2.27621865272522</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G201" t="n">
-        <v>2.27621841430664</v>
+        <v>2.27621865272522</v>
       </c>
       <c r="H201" t="n">
         <v>2500</v>
@@ -6227,7 +6227,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H202" t="n">
         <v>500</v>
@@ -6343,7 +6343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.27621841430664</v>
+        <v>2.27621865272522</v>
       </c>
       <c r="H206" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H207" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G211" t="n">
-        <v>2.23123383522034</v>
+        <v>2.23123407363892</v>
       </c>
       <c r="H211" t="n">
         <v>3500</v>
@@ -6517,7 +6517,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G212" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6546,7 +6546,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>2.2852156162262</v>
+        <v>2.28521537780762</v>
       </c>
       <c r="H213" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>2.5</v>
       </c>
       <c r="G216" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H218" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H219" t="n">
         <v>2500</v>
@@ -6778,7 +6778,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H221" t="n">
         <v>4500</v>
@@ -6807,7 +6807,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H222" t="n">
         <v>500</v>
@@ -6836,7 +6836,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.20424318313599</v>
+        <v>2.20424342155457</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -6981,7 +6981,7 @@
         <v>2.5</v>
       </c>
       <c r="G228" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>2.5</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H229" t="n">
         <v>500</v>
@@ -7039,7 +7039,7 @@
         <v>2.5</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.5</v>
       </c>
       <c r="G231" t="n">
-        <v>2.24922776222229</v>
+        <v>2.24922800064087</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7184,7 +7184,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H235" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>1.97032356262207</v>
+        <v>1.97032368183136</v>
       </c>
       <c r="H241" t="n">
         <v>14000</v>
@@ -7474,7 +7474,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H245" t="n">
         <v>2500</v>
@@ -7503,7 +7503,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7590,7 +7590,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H249" t="n">
         <v>3500</v>
@@ -7619,7 +7619,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H250" t="n">
         <v>1500</v>
@@ -7648,7 +7648,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H251" t="n">
         <v>2500</v>
@@ -7677,7 +7677,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H252" t="n">
         <v>1500</v>
@@ -7706,7 +7706,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>1.98831737041473</v>
+        <v>1.98831748962402</v>
       </c>
       <c r="H253" t="n">
         <v>1500</v>
@@ -7764,7 +7764,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G255" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H255" t="n">
         <v>8500</v>
@@ -7793,7 +7793,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>2.04229879379272</v>
+        <v>2.0422990322113</v>
       </c>
       <c r="H259" t="n">
         <v>1000</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H260" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H261" t="n">
         <v>500</v>
@@ -7967,7 +7967,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G262" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G263" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H264" t="n">
         <v>2500</v>
@@ -8257,7 +8257,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>2.14126515388489</v>
+        <v>2.14126491546631</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H274" t="n">
         <v>1000</v>
@@ -8344,7 +8344,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G280" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G285" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G287" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G288" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>2.13226771354675</v>
+        <v>2.13226795196533</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H290" t="n">
         <v>500</v>
@@ -8924,7 +8924,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>2.11427402496338</v>
+        <v>2.11427426338196</v>
       </c>
       <c r="H295" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.03330206871033</v>
+        <v>2.03330183029175</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>2.06029272079468</v>
+        <v>2.0602924823761</v>
       </c>
       <c r="H299" t="n">
         <v>1000</v>
@@ -9243,7 +9243,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H306" t="n">
         <v>2000</v>
@@ -9272,7 +9272,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G308" t="n">
-        <v>1.96132671833038</v>
+        <v>1.96132683753967</v>
       </c>
       <c r="H308" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G309" t="n">
-        <v>1.96132671833038</v>
+        <v>1.96132683753967</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.88035428524017</v>
+        <v>1.88035440444946</v>
       </c>
       <c r="H310" t="n">
         <v>13500</v>
@@ -9388,7 +9388,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H311" t="n">
         <v>25500</v>
@@ -9417,7 +9417,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G312" t="n">
-        <v>1.88035428524017</v>
+        <v>1.88035440444946</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G313" t="n">
-        <v>1.87135744094849</v>
+        <v>1.87135756015778</v>
       </c>
       <c r="H313" t="n">
         <v>58000</v>
@@ -9475,7 +9475,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G314" t="n">
-        <v>1.87135744094849</v>
+        <v>1.87135756015778</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9678,7 +9678,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H321" t="n">
         <v>1500</v>
@@ -9707,7 +9707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H322" t="n">
         <v>500</v>
@@ -9910,7 +9910,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G329" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H329" t="n">
         <v>500</v>
@@ -9939,7 +9939,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87135744094849</v>
+        <v>1.87135756015778</v>
       </c>
       <c r="H330" t="n">
         <v>2000</v>
@@ -9968,7 +9968,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H331" t="n">
         <v>3000</v>
@@ -9997,7 +9997,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H333" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H336" t="n">
         <v>5000</v>
@@ -10142,7 +10142,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H337" t="n">
         <v>8500</v>
@@ -10374,7 +10374,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H345" t="n">
         <v>2500</v>
@@ -10403,7 +10403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G346" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H347" t="n">
         <v>2500</v>
@@ -10461,7 +10461,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H348" t="n">
         <v>1000</v>
@@ -10490,7 +10490,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G349" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.85336375236511</v>
+        <v>1.85336363315582</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>1.97932064533234</v>
+        <v>1.97932040691376</v>
       </c>
       <c r="H356" t="n">
         <v>3000</v>
@@ -11650,7 +11650,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H389" t="n">
         <v>1000</v>
@@ -11679,7 +11679,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.83536982536316</v>
+        <v>1.83536994457245</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>1.76339471340179</v>
+        <v>1.7633945941925</v>
       </c>
       <c r="H397" t="n">
         <v>18000</v>
@@ -12143,7 +12143,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H406" t="n">
         <v>3500</v>
@@ -12375,7 +12375,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G414" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H414" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G417" t="n">
-        <v>1.50248420238495</v>
+        <v>1.50248408317566</v>
       </c>
       <c r="H417" t="n">
         <v>1500</v>
@@ -12665,7 +12665,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>1.76339471340179</v>
+        <v>1.7633945941925</v>
       </c>
       <c r="H424" t="n">
         <v>5500</v>
@@ -12723,7 +12723,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.78138840198517</v>
+        <v>1.78138852119446</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12752,7 +12752,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G427" t="n">
-        <v>1.81737613677979</v>
+        <v>1.8173760175705</v>
       </c>
       <c r="H427" t="n">
         <v>5500</v>
@@ -12810,7 +12810,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>1.75439774990082</v>
+        <v>1.75439786911011</v>
       </c>
       <c r="H429" t="n">
         <v>1000</v>
@@ -12897,7 +12897,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70941305160522</v>
+        <v>1.70941317081451</v>
       </c>
       <c r="H432" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G438" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H438" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G440" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H440" t="n">
         <v>25000</v>
@@ -13158,7 +13158,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H441" t="n">
         <v>21000</v>
@@ -13303,7 +13303,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G446" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H446" t="n">
         <v>16500</v>
@@ -13332,7 +13332,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G447" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H447" t="n">
         <v>11000</v>
@@ -13361,7 +13361,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G448" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H448" t="n">
         <v>11500</v>
@@ -13390,7 +13390,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H449" t="n">
         <v>9000</v>
@@ -13448,7 +13448,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G451" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H451" t="n">
         <v>25500</v>
@@ -13564,7 +13564,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H455" t="n">
         <v>14500</v>
@@ -13883,7 +13883,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H466" t="n">
         <v>8000</v>
@@ -13970,7 +13970,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H469" t="n">
         <v>25500</v>
@@ -13999,7 +13999,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H470" t="n">
         <v>4000</v>
@@ -14028,7 +14028,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H471" t="n">
         <v>6000</v>
@@ -14086,7 +14086,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H473" t="n">
         <v>5500</v>
@@ -14115,7 +14115,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H474" t="n">
         <v>17500</v>
@@ -14144,7 +14144,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H475" t="n">
         <v>23000</v>
@@ -14173,7 +14173,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G476" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H476" t="n">
         <v>8000</v>
@@ -14231,7 +14231,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G478" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H478" t="n">
         <v>5000</v>
@@ -14376,7 +14376,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G483" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H483" t="n">
         <v>13500</v>
@@ -14405,7 +14405,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G484" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H484" t="n">
         <v>5000</v>
@@ -14492,7 +14492,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G487" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H487" t="n">
         <v>4500</v>
@@ -14521,7 +14521,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G488" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14550,7 +14550,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G489" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G491" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H491" t="n">
         <v>1000</v>
@@ -14637,7 +14637,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G492" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G493" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G494" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H494" t="n">
         <v>1500</v>
@@ -14724,7 +14724,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G495" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H495" t="n">
         <v>1500</v>
@@ -14753,7 +14753,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H496" t="n">
         <v>1500</v>
@@ -14782,7 +14782,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G497" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H497" t="n">
         <v>2500</v>
@@ -14811,7 +14811,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H498" t="n">
         <v>2500</v>
@@ -14840,7 +14840,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G499" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H499" t="n">
         <v>2500</v>
@@ -14869,7 +14869,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G500" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G502" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H502" t="n">
         <v>12500</v>
@@ -14956,7 +14956,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G503" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -14985,7 +14985,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G504" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H504" t="n">
         <v>6000</v>
@@ -15014,7 +15014,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G505" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H505" t="n">
         <v>6000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G506" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G507" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H507" t="n">
         <v>1000</v>
@@ -15101,7 +15101,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G508" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G509" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G510" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G516" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H516" t="n">
         <v>12000</v>
@@ -15362,7 +15362,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G517" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H523" t="n">
         <v>13000</v>
@@ -15594,7 +15594,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H525" t="n">
         <v>7500</v>
@@ -15623,7 +15623,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G526" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H526" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G528" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H529" t="n">
         <v>26500</v>
@@ -15855,7 +15855,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H534" t="n">
         <v>41500</v>
@@ -15884,7 +15884,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H535" t="n">
         <v>5500</v>
@@ -15942,7 +15942,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H537" t="n">
         <v>2500</v>
@@ -16087,7 +16087,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H544" t="n">
         <v>500</v>
@@ -16174,7 +16174,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G546" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>0.908688068389893</v>
+        <v>0.908688008785248</v>
       </c>
       <c r="H548" t="n">
         <v>6500</v>
@@ -16435,7 +16435,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G554" t="n">
-        <v>0.760239005088806</v>
+        <v>0.760239064693451</v>
       </c>
       <c r="H554" t="n">
         <v>59000</v>
@@ -16580,7 +16580,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G559" t="n">
-        <v>0.710756063461304</v>
+        <v>0.710756003856659</v>
       </c>
       <c r="H559" t="n">
         <v>6500</v>
@@ -16609,7 +16609,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G560" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H560" t="n">
         <v>11500</v>
@@ -16638,7 +16638,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G561" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G563" t="n">
-        <v>0.719752907752991</v>
+        <v>0.719752967357635</v>
       </c>
       <c r="H563" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G565" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H565" t="n">
         <v>5500</v>
@@ -16783,7 +16783,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.724251389503479</v>
+        <v>0.724251329898834</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G569" t="n">
-        <v>0.620786845684052</v>
+        <v>0.620786905288696</v>
       </c>
       <c r="H569" t="n">
         <v>62000</v>
@@ -16899,7 +16899,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G570" t="n">
-        <v>0.589297652244568</v>
+        <v>0.589297711849213</v>
       </c>
       <c r="H570" t="n">
         <v>10000</v>
@@ -17015,7 +17015,7 @@
         <v>0.625</v>
       </c>
       <c r="G574" t="n">
-        <v>0.562306940555573</v>
+        <v>0.562307000160217</v>
       </c>
       <c r="H574" t="n">
         <v>27500</v>
@@ -17189,7 +17189,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G580" t="n">
-        <v>0.620786845684052</v>
+        <v>0.620786905288696</v>
       </c>
       <c r="H580" t="n">
         <v>149500</v>
@@ -17334,7 +17334,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H585" t="n">
         <v>427500</v>
@@ -17479,7 +17479,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G590" t="n">
-        <v>0.760239005088806</v>
+        <v>0.760239064693451</v>
       </c>
       <c r="H590" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G599" t="n">
-        <v>0.836712777614594</v>
+        <v>0.836712718009949</v>
       </c>
       <c r="H599" t="n">
         <v>16000</v>
@@ -17914,7 +17914,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H605" t="n">
         <v>35500</v>
@@ -17943,7 +17943,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H606" t="n">
         <v>4000</v>
@@ -17972,7 +17972,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G607" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>0.769235968589783</v>
+        <v>0.769235908985138</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G614" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H614" t="n">
         <v>210000</v>
@@ -18320,7 +18320,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G619" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H619" t="n">
         <v>26500</v>
@@ -18378,7 +18378,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G621" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G622" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H622" t="n">
         <v>20500</v>
@@ -18465,7 +18465,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H624" t="n">
         <v>40500</v>
@@ -18494,7 +18494,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H625" t="n">
         <v>3000</v>
@@ -18552,7 +18552,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>0.908688068389893</v>
+        <v>0.908688008785248</v>
       </c>
       <c r="H627" t="n">
         <v>28000</v>
@@ -18581,7 +18581,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>0.890694200992584</v>
+        <v>0.890694260597229</v>
       </c>
       <c r="H628" t="n">
         <v>11500</v>
@@ -18610,7 +18610,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>0.881697356700897</v>
+        <v>0.881697297096252</v>
       </c>
       <c r="H629" t="n">
         <v>5000</v>
@@ -18639,7 +18639,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>0.881697356700897</v>
+        <v>0.881697297096252</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18697,7 +18697,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H632" t="n">
         <v>23000</v>
@@ -18726,7 +18726,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H633" t="n">
         <v>17000</v>
@@ -18755,7 +18755,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H634" t="n">
         <v>4000</v>
@@ -18784,7 +18784,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H635" t="n">
         <v>3000</v>
@@ -18813,7 +18813,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>0.953672587871552</v>
+        <v>0.953672528266907</v>
       </c>
       <c r="H636" t="n">
         <v>17500</v>
@@ -18842,7 +18842,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G637" t="n">
-        <v>0.989660322666168</v>
+        <v>0.989660203456879</v>
       </c>
       <c r="H637" t="n">
         <v>43000</v>
@@ -19451,7 +19451,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H658" t="n">
         <v>2500</v>
@@ -19509,7 +19509,7 @@
         <v>1.25</v>
       </c>
       <c r="G660" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H660" t="n">
         <v>12500</v>
@@ -19567,7 +19567,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G662" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19596,7 +19596,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H663" t="n">
         <v>5500</v>
@@ -19625,7 +19625,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H665" t="n">
         <v>27000</v>
@@ -19799,7 +19799,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G670" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19886,7 +19886,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H673" t="n">
         <v>30500</v>
@@ -19944,7 +19944,7 @@
         <v>1.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H675" t="n">
         <v>10500</v>
@@ -19973,7 +19973,7 @@
         <v>1.25</v>
       </c>
       <c r="G676" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H676" t="n">
         <v>7000</v>
@@ -20147,7 +20147,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H682" t="n">
         <v>12000</v>
@@ -20234,7 +20234,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H685" t="n">
         <v>1000</v>
@@ -20263,7 +20263,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H686" t="n">
         <v>4000</v>
@@ -20553,7 +20553,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H696" t="n">
         <v>31000</v>
@@ -20814,7 +20814,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G705" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H705" t="n">
         <v>39500</v>
@@ -20988,7 +20988,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H711" t="n">
         <v>9500</v>
@@ -21017,7 +21017,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G712" t="n">
-        <v>1.50248420238495</v>
+        <v>1.50248408317566</v>
       </c>
       <c r="H712" t="n">
         <v>18500</v>
@@ -21162,7 +21162,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G717" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H717" t="n">
         <v>3000</v>
@@ -21249,7 +21249,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G720" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H720" t="n">
         <v>25500</v>
@@ -21307,7 +21307,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G722" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H722" t="n">
         <v>13500</v>
@@ -21336,7 +21336,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H723" t="n">
         <v>8000</v>
@@ -21423,7 +21423,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G726" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H726" t="n">
         <v>1000</v>
@@ -21452,7 +21452,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G727" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H727" t="n">
         <v>16000</v>
@@ -21481,7 +21481,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H730" t="n">
         <v>3500</v>
@@ -21684,7 +21684,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G735" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H735" t="n">
         <v>14000</v>
@@ -21916,7 +21916,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G743" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H743" t="n">
         <v>14500</v>
@@ -22119,7 +22119,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G750" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H750" t="n">
         <v>32500</v>
@@ -23250,7 +23250,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G789" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H789" t="n">
         <v>32000</v>
@@ -23308,7 +23308,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G791" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H791" t="n">
         <v>1000</v>
@@ -23656,7 +23656,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G803" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H803" t="n">
         <v>18500</v>
@@ -23685,7 +23685,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G804" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H804" t="n">
         <v>5000</v>
@@ -24091,7 +24091,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G818" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H818" t="n">
         <v>10000</v>
@@ -24120,7 +24120,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G819" t="n">
-        <v>1.44850277900696</v>
+        <v>1.44850265979767</v>
       </c>
       <c r="H819" t="n">
         <v>6000</v>
@@ -24410,7 +24410,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H829" t="n">
         <v>3000</v>
@@ -24439,7 +24439,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H830" t="n">
         <v>2000</v>
@@ -24584,7 +24584,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.53847193717957</v>
+        <v>1.53847181797028</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -24758,7 +24758,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G841" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H841" t="n">
         <v>14500</v>
@@ -24845,7 +24845,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G844" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H844" t="n">
         <v>17500</v>
@@ -24903,7 +24903,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G846" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H846" t="n">
         <v>18500</v>
@@ -25077,7 +25077,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H852" t="n">
         <v>12500</v>
@@ -25309,7 +25309,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G860" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H860" t="n">
         <v>3500</v>
@@ -25338,7 +25338,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G861" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H861" t="n">
         <v>3000</v>
@@ -25367,7 +25367,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G870" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H870" t="n">
         <v>2500</v>
@@ -25628,7 +25628,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G871" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H871" t="n">
         <v>6500</v>
@@ -25657,7 +25657,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G872" t="n">
-        <v>1.430508852005</v>
+        <v>1.43050897121429</v>
       </c>
       <c r="H872" t="n">
         <v>8000</v>
@@ -25744,7 +25744,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H875" t="n">
         <v>500</v>
@@ -25773,7 +25773,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H876" t="n">
         <v>7500</v>
@@ -25802,7 +25802,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H877" t="n">
         <v>1000</v>
@@ -25831,7 +25831,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G878" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26092,7 +26092,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G887" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H887" t="n">
         <v>1000</v>
@@ -26121,7 +26121,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G888" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G889" t="n">
-        <v>1.42151212692261</v>
+        <v>1.42151200771332</v>
       </c>
       <c r="H889" t="n">
         <v>1500</v>
@@ -26759,7 +26759,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.17859530448914</v>
+        <v>1.17859542369843</v>
       </c>
       <c r="H910" t="n">
         <v>8000</v>
@@ -26904,7 +26904,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -26991,7 +26991,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G918" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H918" t="n">
         <v>9500</v>
@@ -27049,7 +27049,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27107,7 +27107,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G922" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H922" t="n">
         <v>500</v>
@@ -27136,7 +27136,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H923" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G925" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H925" t="n">
         <v>3500</v>
@@ -27223,7 +27223,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G926" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G929" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H929" t="n">
         <v>22000</v>
@@ -27455,7 +27455,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G934" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H934" t="n">
         <v>8000</v>
@@ -27484,7 +27484,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G935" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H935" t="n">
         <v>5500</v>
@@ -27513,7 +27513,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G936" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>1.20108771324158</v>
+        <v>1.20108759403229</v>
       </c>
       <c r="H938" t="n">
         <v>3500</v>
@@ -27600,7 +27600,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>1.20108771324158</v>
+        <v>1.20108759403229</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G961" t="n">
-        <v>1.2910567522049</v>
+        <v>1.29105663299561</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28325,7 +28325,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G964" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H964" t="n">
         <v>5000</v>
@@ -28557,7 +28557,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G972" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H972" t="n">
         <v>3500</v>
@@ -28644,7 +28644,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H975" t="n">
         <v>1000</v>
@@ -28673,7 +28673,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H976" t="n">
         <v>2000</v>
@@ -28702,7 +28702,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H978" t="n">
         <v>1000</v>
@@ -28818,7 +28818,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G981" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H981" t="n">
         <v>2500</v>
@@ -28963,7 +28963,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G986" t="n">
-        <v>1.17409694194794</v>
+        <v>1.17409682273865</v>
       </c>
       <c r="H986" t="n">
         <v>6500</v>
@@ -28992,7 +28992,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G987" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H987" t="n">
         <v>500</v>
@@ -29021,7 +29021,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G988" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -29050,7 +29050,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G989" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G990" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G992" t="n">
-        <v>1.1920907497406</v>
+        <v>1.19209086894989</v>
       </c>
       <c r="H992" t="n">
         <v>1000</v>
@@ -29166,7 +29166,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G993" t="n">
-        <v>1.1920907497406</v>
+        <v>1.19209086894989</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>1.1920907497406</v>
+        <v>1.19209086894989</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G997" t="n">
-        <v>1.17859530448914</v>
+        <v>1.17859542369843</v>
       </c>
       <c r="H997" t="n">
         <v>500</v>
@@ -29340,7 +29340,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G999" t="n">
-        <v>1.12011551856995</v>
+        <v>1.12011539936066</v>
       </c>
       <c r="H999" t="n">
         <v>4500</v>
@@ -29514,7 +29514,7 @@
         <v>1.25</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1005" t="n">
         <v>1500</v>
@@ -29543,7 +29543,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1006" t="n">
         <v>9000</v>
@@ -29601,7 +29601,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29630,7 +29630,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1009" t="n">
         <v>9500</v>
@@ -29659,7 +29659,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1011" t="n">
         <v>2500</v>
@@ -29717,7 +29717,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -29775,7 +29775,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.1426078081131</v>
+        <v>1.14260768890381</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>1.25</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1022" t="n">
         <v>4000</v>
@@ -30036,7 +30036,7 @@
         <v>1.25</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1023" t="n">
         <v>1500</v>
@@ -30065,7 +30065,7 @@
         <v>1.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1031" t="n">
         <v>11500</v>
@@ -30297,7 +30297,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -30326,7 +30326,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10662019252777</v>
+        <v>1.10662007331848</v>
       </c>
       <c r="H1033" t="n">
         <v>3000</v>
@@ -30384,7 +30384,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.12011551856995</v>
+        <v>1.12011539936066</v>
       </c>
       <c r="H1035" t="n">
         <v>500</v>
@@ -30442,7 +30442,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H1037" t="n">
         <v>3000</v>
@@ -30558,7 +30558,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1041" t="n">
         <v>7500</v>
@@ -30674,7 +30674,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1045" t="n">
         <v>1000</v>
@@ -30703,7 +30703,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1052" t="n">
         <v>2000</v>
@@ -30993,7 +30993,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H1056" t="n">
         <v>6000</v>
@@ -31080,7 +31080,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1059" t="n">
         <v>500</v>
@@ -31109,7 +31109,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1060" t="n">
         <v>2500</v>
@@ -31138,7 +31138,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31167,7 +31167,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31196,7 +31196,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.91768491268158</v>
+        <v>0.917684972286224</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1064" t="n">
         <v>4000</v>
@@ -31254,7 +31254,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.926681876182556</v>
+        <v>0.926681816577911</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -31283,7 +31283,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1066" t="n">
         <v>500</v>
@@ -31312,7 +31312,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -31341,7 +31341,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -31399,7 +31399,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.949174046516418</v>
+        <v>0.949174106121063</v>
       </c>
       <c r="H1070" t="n">
         <v>7500</v>
@@ -31457,7 +31457,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1072" t="n">
         <v>4000</v>
@@ -31486,7 +31486,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.980663359165192</v>
+        <v>0.980663418769836</v>
       </c>
       <c r="H1073" t="n">
         <v>500</v>
@@ -31544,7 +31544,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1075" t="n">
         <v>1500</v>
@@ -31573,7 +31573,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1076" t="n">
         <v>500</v>
@@ -31602,7 +31602,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.935678720474243</v>
+        <v>0.935678780078888</v>
       </c>
       <c r="H1077" t="n">
         <v>13500</v>
@@ -31776,7 +31776,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1083" t="n">
         <v>1000</v>
@@ -31805,7 +31805,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31834,7 +31834,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1085" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1086" t="n">
         <v>0</v>
@@ -31892,7 +31892,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1087" t="n">
         <v>0</v>
@@ -31921,7 +31921,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.99865710735321</v>
+        <v>0.998657166957855</v>
       </c>
       <c r="H1088" t="n">
         <v>3500</v>
@@ -32008,7 +32008,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1091" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>1.25</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1092" t="n">
         <v>1000</v>
@@ -32791,7 +32791,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H1118" t="n">
         <v>2000</v>
@@ -32936,7 +32936,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1123" t="n">
         <v>6500</v>
@@ -32965,7 +32965,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1124" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.07063257694244</v>
+        <v>1.07063245773315</v>
       </c>
       <c r="H1136" t="n">
         <v>2500</v>
@@ -33342,7 +33342,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1137" t="n">
         <v>2500</v>
@@ -33371,7 +33371,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1138" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1139" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.05713701248169</v>
+        <v>1.05713713169098</v>
       </c>
       <c r="H1140" t="n">
         <v>0</v>
@@ -33487,7 +33487,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.03014636039734</v>
+        <v>1.03014624118805</v>
       </c>
       <c r="H1143" t="n">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.01665103435516</v>
+        <v>1.01665091514587</v>
       </c>
       <c r="H1145" t="n">
         <v>8000</v>
@@ -33719,7 +33719,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.11561691761017</v>
+        <v>1.11561703681946</v>
       </c>
       <c r="H1150" t="n">
         <v>8000</v>
@@ -33777,7 +33777,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H1152" t="n">
         <v>19500</v>
@@ -33835,7 +33835,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.21008467674255</v>
+        <v>1.21008455753326</v>
       </c>
       <c r="H1154" t="n">
         <v>6500</v>
@@ -33864,7 +33864,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H1155" t="n">
         <v>10500</v>
@@ -34067,7 +34067,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1162" t="n">
         <v>23000</v>
@@ -34096,7 +34096,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1163" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1164" t="n">
         <v>2500</v>
@@ -34183,7 +34183,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H1166" t="n">
         <v>17000</v>
@@ -34386,7 +34386,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.22358000278473</v>
+        <v>1.22357988357544</v>
       </c>
       <c r="H1173" t="n">
         <v>5500</v>
@@ -34415,7 +34415,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1174" t="n">
         <v>5500</v>
@@ -34444,7 +34444,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1176" t="n">
         <v>500</v>
@@ -34589,7 +34589,7 @@
         <v>1.25</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.12461388111115</v>
+        <v>1.12461400032043</v>
       </c>
       <c r="H1180" t="n">
         <v>19500</v>
@@ -34647,7 +34647,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1182" t="n">
         <v>10000</v>
@@ -34676,7 +34676,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.10212159156799</v>
+        <v>1.10212171077728</v>
       </c>
       <c r="H1183" t="n">
         <v>45500</v>
@@ -34763,7 +34763,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.25506901741028</v>
+        <v>1.25506913661957</v>
       </c>
       <c r="H1186" t="n">
         <v>52000</v>
@@ -34821,7 +34821,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.1875923871994</v>
+        <v>1.18759226799011</v>
       </c>
       <c r="H1188" t="n">
         <v>1000</v>
@@ -34850,7 +34850,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.20558607578278</v>
+        <v>1.20558619499207</v>
       </c>
       <c r="H1189" t="n">
         <v>53000</v>
@@ -35024,7 +35024,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H1195" t="n">
         <v>5000</v>
@@ -35053,7 +35053,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.2415736913681</v>
+        <v>1.24157381057739</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1197" t="n">
         <v>76000</v>
@@ -35111,7 +35111,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.43950581550598</v>
+        <v>1.43950593471527</v>
       </c>
       <c r="H1198" t="n">
         <v>85500</v>
@@ -35256,7 +35256,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1203" t="n">
         <v>8500</v>
@@ -35285,7 +35285,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.35853362083435</v>
+        <v>1.35853350162506</v>
       </c>
       <c r="H1204" t="n">
         <v>0</v>
@@ -61072,6 +61072,35 @@
         <v>2500</v>
       </c>
       <c r="I2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2094" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I2094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VIM.MI.xlsx
+++ b/data/VIM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05804991722107</v>
+        <v>3.05805015563965</v>
       </c>
       <c r="H3" t="n">
         <v>192000</v>
@@ -485,7 +485,7 @@
         <v>3.4284999370575</v>
       </c>
       <c r="G4" t="n">
-        <v>3.08459115028381</v>
+        <v>3.08459091186523</v>
       </c>
       <c r="H4" t="n">
         <v>184000</v>
@@ -630,7 +630,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05850005149841</v>
+        <v>3.05849981307983</v>
       </c>
       <c r="H9" t="n">
         <v>8500</v>
@@ -688,7 +688,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05850005149841</v>
+        <v>3.05849981307983</v>
       </c>
       <c r="H11" t="n">
         <v>4000</v>
@@ -717,7 +717,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05445146560669</v>
+        <v>3.05445122718811</v>
       </c>
       <c r="H12" t="n">
         <v>9000</v>
@@ -775,7 +775,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0409562587738</v>
+        <v>3.04095602035522</v>
       </c>
       <c r="H14" t="n">
         <v>3000</v>
@@ -978,7 +978,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>3.0409562587738</v>
+        <v>3.04095602035522</v>
       </c>
       <c r="H21" t="n">
         <v>24500</v>
@@ -1268,7 +1268,7 @@
         <v>3.21050000190735</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8884584903717</v>
+        <v>2.88845825195312</v>
       </c>
       <c r="H31" t="n">
         <v>16500</v>
@@ -1616,7 +1616,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H43" t="n">
         <v>3500</v>
@@ -1645,7 +1645,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G45" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G46" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>3.21749997138977</v>
       </c>
       <c r="G48" t="n">
-        <v>2.89475607872009</v>
+        <v>2.89475631713867</v>
       </c>
       <c r="H48" t="n">
         <v>11000</v>
@@ -1790,7 +1790,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>2.90510272979736</v>
+        <v>2.90510296821594</v>
       </c>
       <c r="H49" t="n">
         <v>3500</v>
@@ -1819,7 +1819,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.90510272979736</v>
+        <v>2.90510296821594</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G51" t="n">
-        <v>2.87856197357178</v>
+        <v>2.8785617351532</v>
       </c>
       <c r="H51" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G52" t="n">
-        <v>2.87856197357178</v>
+        <v>2.8785617351532</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.19950008392334</v>
       </c>
       <c r="G53" t="n">
-        <v>2.87856197357178</v>
+        <v>2.8785617351532</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3.21449995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89205718040466</v>
+        <v>2.89205694198608</v>
       </c>
       <c r="H54" t="n">
         <v>2500</v>
@@ -2138,7 +2138,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G61" t="n">
-        <v>2.87901186943054</v>
+        <v>2.87901163101196</v>
       </c>
       <c r="H61" t="n">
         <v>10000</v>
@@ -2167,7 +2167,7 @@
         <v>3.18350005149841</v>
       </c>
       <c r="G62" t="n">
-        <v>2.86416673660278</v>
+        <v>2.86416697502136</v>
       </c>
       <c r="H62" t="n">
         <v>8500</v>
@@ -2486,7 +2486,7 @@
         <v>3.05100011825562</v>
       </c>
       <c r="G73" t="n">
-        <v>2.74495792388916</v>
+        <v>2.74495768547058</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2660,7 +2660,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.69007635116577</v>
+        <v>2.69007658958435</v>
       </c>
       <c r="H79" t="n">
         <v>4500</v>
@@ -2689,7 +2689,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>2.69007635116577</v>
+        <v>2.69007658958435</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.69007635116577</v>
+        <v>2.69007658958435</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G88" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G92" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G94" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G96" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>3.09850001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>2.78769278526306</v>
+        <v>2.78769302368164</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>3.02649998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7229151725769</v>
+        <v>2.72291541099548</v>
       </c>
       <c r="H109" t="n">
         <v>500</v>
@@ -4197,7 +4197,7 @@
         <v>2.81949996948242</v>
       </c>
       <c r="G132" t="n">
-        <v>2.53667902946472</v>
+        <v>2.5366792678833</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4284,7 +4284,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>2.42016911506653</v>
+        <v>2.42016935348511</v>
       </c>
       <c r="H135" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>2.14126491546631</v>
+        <v>2.14126515388489</v>
       </c>
       <c r="H155" t="n">
         <v>8000</v>
@@ -4893,7 +4893,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G156" t="n">
-        <v>2.14126491546631</v>
+        <v>2.14126515388489</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G160" t="n">
-        <v>2.0863835811615</v>
+        <v>2.08638381958008</v>
       </c>
       <c r="H160" t="n">
         <v>2000</v>
@@ -5038,7 +5038,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5154,7 +5154,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G165" t="n">
-        <v>2.0863835811615</v>
+        <v>2.08638381958008</v>
       </c>
       <c r="H165" t="n">
         <v>1000</v>
@@ -5531,7 +5531,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H178" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H180" t="n">
         <v>3000</v>
@@ -5850,7 +5850,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.24023079872131</v>
+        <v>2.24023103713989</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.24023079872131</v>
+        <v>2.24023103713989</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35719084739685</v>
+        <v>2.35719060897827</v>
       </c>
       <c r="H193" t="n">
         <v>9500</v>
@@ -5995,7 +5995,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38418173789978</v>
+        <v>2.3841814994812</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6169,7 +6169,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G200" t="n">
-        <v>2.27621865272522</v>
+        <v>2.27621841430664</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G201" t="n">
-        <v>2.27621865272522</v>
+        <v>2.27621841430664</v>
       </c>
       <c r="H201" t="n">
         <v>2500</v>
@@ -6227,7 +6227,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H202" t="n">
         <v>500</v>
@@ -6343,7 +6343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.27621865272522</v>
+        <v>2.27621841430664</v>
       </c>
       <c r="H206" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H207" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G211" t="n">
-        <v>2.23123407363892</v>
+        <v>2.23123383522034</v>
       </c>
       <c r="H211" t="n">
         <v>3500</v>
@@ -6517,7 +6517,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G212" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6546,7 +6546,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>2.28521537780762</v>
+        <v>2.2852156162262</v>
       </c>
       <c r="H213" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>2.5</v>
       </c>
       <c r="G216" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H218" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H219" t="n">
         <v>2500</v>
@@ -6778,7 +6778,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G221" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H221" t="n">
         <v>4500</v>
@@ -6807,7 +6807,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G222" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H222" t="n">
         <v>500</v>
@@ -6836,7 +6836,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G225" t="n">
-        <v>2.20424342155457</v>
+        <v>2.20424318313599</v>
       </c>
       <c r="H225" t="n">
         <v>5000</v>
@@ -6981,7 +6981,7 @@
         <v>2.5</v>
       </c>
       <c r="G228" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>2.5</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H229" t="n">
         <v>500</v>
@@ -7039,7 +7039,7 @@
         <v>2.5</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.5</v>
       </c>
       <c r="G231" t="n">
-        <v>2.24922800064087</v>
+        <v>2.24922776222229</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7184,7 +7184,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H235" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>1.97032368183136</v>
+        <v>1.97032356262207</v>
       </c>
       <c r="H241" t="n">
         <v>14000</v>
@@ -7474,7 +7474,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H245" t="n">
         <v>2500</v>
@@ -7503,7 +7503,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G246" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7590,7 +7590,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H249" t="n">
         <v>3500</v>
@@ -7619,7 +7619,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H250" t="n">
         <v>1500</v>
@@ -7648,7 +7648,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H251" t="n">
         <v>2500</v>
@@ -7677,7 +7677,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H252" t="n">
         <v>1500</v>
@@ -7706,7 +7706,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>1.98831748962402</v>
+        <v>1.98831737041473</v>
       </c>
       <c r="H253" t="n">
         <v>1500</v>
@@ -7764,7 +7764,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G255" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H255" t="n">
         <v>8500</v>
@@ -7793,7 +7793,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H256" t="n">
         <v>1500</v>
@@ -7822,7 +7822,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0422990322113</v>
+        <v>2.04229879379272</v>
       </c>
       <c r="H259" t="n">
         <v>1000</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H260" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H261" t="n">
         <v>500</v>
@@ -7967,7 +7967,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G262" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G263" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H264" t="n">
         <v>2500</v>
@@ -8257,7 +8257,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>2.14126491546631</v>
+        <v>2.14126515388489</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H274" t="n">
         <v>1000</v>
@@ -8344,7 +8344,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G280" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G283" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G285" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G287" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G288" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>2.13226795196533</v>
+        <v>2.13226771354675</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H290" t="n">
         <v>500</v>
@@ -8924,7 +8924,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>2.11427426338196</v>
+        <v>2.11427402496338</v>
       </c>
       <c r="H295" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.03330183029175</v>
+        <v>2.03330206871033</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>2.0602924823761</v>
+        <v>2.06029272079468</v>
       </c>
       <c r="H299" t="n">
         <v>1000</v>
@@ -9243,7 +9243,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G306" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H306" t="n">
         <v>2000</v>
@@ -9272,7 +9272,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G308" t="n">
-        <v>1.96132683753967</v>
+        <v>1.96132671833038</v>
       </c>
       <c r="H308" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G309" t="n">
-        <v>1.96132683753967</v>
+        <v>1.96132671833038</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.88035440444946</v>
+        <v>1.88035428524017</v>
       </c>
       <c r="H310" t="n">
         <v>13500</v>
@@ -9388,7 +9388,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H311" t="n">
         <v>25500</v>
@@ -9417,7 +9417,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G312" t="n">
-        <v>1.88035440444946</v>
+        <v>1.88035428524017</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G313" t="n">
-        <v>1.87135756015778</v>
+        <v>1.87135744094849</v>
       </c>
       <c r="H313" t="n">
         <v>58000</v>
@@ -9475,7 +9475,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G314" t="n">
-        <v>1.87135756015778</v>
+        <v>1.87135744094849</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9678,7 +9678,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H321" t="n">
         <v>1500</v>
@@ -9707,7 +9707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H322" t="n">
         <v>500</v>
@@ -9910,7 +9910,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G329" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H329" t="n">
         <v>500</v>
@@ -9939,7 +9939,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87135756015778</v>
+        <v>1.87135744094849</v>
       </c>
       <c r="H330" t="n">
         <v>2000</v>
@@ -9968,7 +9968,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H331" t="n">
         <v>3000</v>
@@ -9997,7 +9997,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G333" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H333" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H336" t="n">
         <v>5000</v>
@@ -10142,7 +10142,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H337" t="n">
         <v>8500</v>
@@ -10374,7 +10374,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H345" t="n">
         <v>2500</v>
@@ -10403,7 +10403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G346" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H347" t="n">
         <v>2500</v>
@@ -10461,7 +10461,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H348" t="n">
         <v>1000</v>
@@ -10490,7 +10490,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G349" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.85336363315582</v>
+        <v>1.85336375236511</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>1.97932040691376</v>
+        <v>1.97932064533234</v>
       </c>
       <c r="H356" t="n">
         <v>3000</v>
@@ -11650,7 +11650,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H389" t="n">
         <v>1000</v>
@@ -11679,7 +11679,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.83536994457245</v>
+        <v>1.83536982536316</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>1.7633945941925</v>
+        <v>1.76339471340179</v>
       </c>
       <c r="H397" t="n">
         <v>18000</v>
@@ -12143,7 +12143,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G406" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H406" t="n">
         <v>3500</v>
@@ -12375,7 +12375,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G414" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H414" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G417" t="n">
-        <v>1.50248408317566</v>
+        <v>1.50248420238495</v>
       </c>
       <c r="H417" t="n">
         <v>1500</v>
@@ -12665,7 +12665,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>1.7633945941925</v>
+        <v>1.76339471340179</v>
       </c>
       <c r="H424" t="n">
         <v>5500</v>
@@ -12723,7 +12723,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.78138852119446</v>
+        <v>1.78138840198517</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12752,7 +12752,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G427" t="n">
-        <v>1.8173760175705</v>
+        <v>1.81737613677979</v>
       </c>
       <c r="H427" t="n">
         <v>5500</v>
@@ -12810,7 +12810,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G429" t="n">
-        <v>1.75439786911011</v>
+        <v>1.75439774990082</v>
       </c>
       <c r="H429" t="n">
         <v>1000</v>
@@ -12897,7 +12897,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70941317081451</v>
+        <v>1.70941305160522</v>
       </c>
       <c r="H432" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G438" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H438" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G440" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H440" t="n">
         <v>25000</v>
@@ -13158,7 +13158,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H441" t="n">
         <v>21000</v>
@@ -13303,7 +13303,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G446" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H446" t="n">
         <v>16500</v>
@@ -13332,7 +13332,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G447" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H447" t="n">
         <v>11000</v>
@@ -13361,7 +13361,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G448" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H448" t="n">
         <v>11500</v>
@@ -13390,7 +13390,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H449" t="n">
         <v>9000</v>
@@ -13448,7 +13448,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G451" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H451" t="n">
         <v>25500</v>
@@ -13564,7 +13564,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H455" t="n">
         <v>14500</v>
@@ -13883,7 +13883,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H466" t="n">
         <v>8000</v>
@@ -13970,7 +13970,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H469" t="n">
         <v>25500</v>
@@ -13999,7 +13999,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H470" t="n">
         <v>4000</v>
@@ -14028,7 +14028,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H471" t="n">
         <v>6000</v>
@@ -14086,7 +14086,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H473" t="n">
         <v>5500</v>
@@ -14115,7 +14115,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H474" t="n">
         <v>17500</v>
@@ -14144,7 +14144,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H475" t="n">
         <v>23000</v>
@@ -14173,7 +14173,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G476" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H476" t="n">
         <v>8000</v>
@@ -14231,7 +14231,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G478" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H478" t="n">
         <v>5000</v>
@@ -14376,7 +14376,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G483" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H483" t="n">
         <v>13500</v>
@@ -14405,7 +14405,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G484" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H484" t="n">
         <v>5000</v>
@@ -14492,7 +14492,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G487" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H487" t="n">
         <v>4500</v>
@@ -14521,7 +14521,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G488" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14550,7 +14550,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G489" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G491" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H491" t="n">
         <v>1000</v>
@@ -14637,7 +14637,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G492" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G493" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G494" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H494" t="n">
         <v>1500</v>
@@ -14724,7 +14724,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G495" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H495" t="n">
         <v>1500</v>
@@ -14753,7 +14753,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H496" t="n">
         <v>1500</v>
@@ -14782,7 +14782,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G497" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H497" t="n">
         <v>2500</v>
@@ -14811,7 +14811,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H498" t="n">
         <v>2500</v>
@@ -14840,7 +14840,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G499" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H499" t="n">
         <v>2500</v>
@@ -14869,7 +14869,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G500" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G502" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H502" t="n">
         <v>12500</v>
@@ -14956,7 +14956,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G503" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -14985,7 +14985,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G504" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H504" t="n">
         <v>6000</v>
@@ -15014,7 +15014,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G505" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H505" t="n">
         <v>6000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G506" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G507" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H507" t="n">
         <v>1000</v>
@@ -15101,7 +15101,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G508" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G509" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G510" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G516" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H516" t="n">
         <v>12000</v>
@@ -15362,7 +15362,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G517" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H523" t="n">
         <v>13000</v>
@@ -15594,7 +15594,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H525" t="n">
         <v>7500</v>
@@ -15623,7 +15623,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G526" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H526" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G528" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H529" t="n">
         <v>26500</v>
@@ -15855,7 +15855,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G534" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H534" t="n">
         <v>41500</v>
@@ -15884,7 +15884,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H535" t="n">
         <v>5500</v>
@@ -15942,7 +15942,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H537" t="n">
         <v>2500</v>
@@ -16087,7 +16087,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H544" t="n">
         <v>500</v>
@@ -16174,7 +16174,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G546" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>0.908688008785248</v>
+        <v>0.908688068389893</v>
       </c>
       <c r="H548" t="n">
         <v>6500</v>
@@ -16435,7 +16435,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G554" t="n">
-        <v>0.760239064693451</v>
+        <v>0.760239005088806</v>
       </c>
       <c r="H554" t="n">
         <v>59000</v>
@@ -16580,7 +16580,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G559" t="n">
-        <v>0.710756003856659</v>
+        <v>0.710756063461304</v>
       </c>
       <c r="H559" t="n">
         <v>6500</v>
@@ -16609,7 +16609,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G560" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H560" t="n">
         <v>11500</v>
@@ -16638,7 +16638,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G561" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G563" t="n">
-        <v>0.719752967357635</v>
+        <v>0.719752907752991</v>
       </c>
       <c r="H563" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G565" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H565" t="n">
         <v>5500</v>
@@ -16783,7 +16783,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G566" t="n">
-        <v>0.724251329898834</v>
+        <v>0.724251389503479</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G569" t="n">
-        <v>0.620786905288696</v>
+        <v>0.620786845684052</v>
       </c>
       <c r="H569" t="n">
         <v>62000</v>
@@ -16899,7 +16899,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G570" t="n">
-        <v>0.589297711849213</v>
+        <v>0.589297652244568</v>
       </c>
       <c r="H570" t="n">
         <v>10000</v>
@@ -17015,7 +17015,7 @@
         <v>0.625</v>
       </c>
       <c r="G574" t="n">
-        <v>0.562307000160217</v>
+        <v>0.562306940555573</v>
       </c>
       <c r="H574" t="n">
         <v>27500</v>
@@ -17189,7 +17189,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G580" t="n">
-        <v>0.620786905288696</v>
+        <v>0.620786845684052</v>
       </c>
       <c r="H580" t="n">
         <v>149500</v>
@@ -17334,7 +17334,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H585" t="n">
         <v>427500</v>
@@ -17479,7 +17479,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G590" t="n">
-        <v>0.760239064693451</v>
+        <v>0.760239005088806</v>
       </c>
       <c r="H590" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G599" t="n">
-        <v>0.836712718009949</v>
+        <v>0.836712777614594</v>
       </c>
       <c r="H599" t="n">
         <v>16000</v>
@@ -17914,7 +17914,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G605" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H605" t="n">
         <v>35500</v>
@@ -17943,7 +17943,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H606" t="n">
         <v>4000</v>
@@ -17972,7 +17972,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G607" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>0.769235908985138</v>
+        <v>0.769235968589783</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G614" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H614" t="n">
         <v>210000</v>
@@ -18320,7 +18320,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G619" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H619" t="n">
         <v>26500</v>
@@ -18378,7 +18378,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G621" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G622" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H622" t="n">
         <v>20500</v>
@@ -18465,7 +18465,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H624" t="n">
         <v>40500</v>
@@ -18494,7 +18494,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H625" t="n">
         <v>3000</v>
@@ -18552,7 +18552,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>0.908688008785248</v>
+        <v>0.908688068389893</v>
       </c>
       <c r="H627" t="n">
         <v>28000</v>
@@ -18581,7 +18581,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>0.890694260597229</v>
+        <v>0.890694200992584</v>
       </c>
       <c r="H628" t="n">
         <v>11500</v>
@@ -18610,7 +18610,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>0.881697297096252</v>
+        <v>0.881697356700897</v>
       </c>
       <c r="H629" t="n">
         <v>5000</v>
@@ -18639,7 +18639,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>0.881697297096252</v>
+        <v>0.881697356700897</v>
       </c>
       <c r="H630" t="n">
         <v>5000</v>
@@ -18668,7 +18668,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18697,7 +18697,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H632" t="n">
         <v>23000</v>
@@ -18726,7 +18726,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H633" t="n">
         <v>17000</v>
@@ -18755,7 +18755,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H634" t="n">
         <v>4000</v>
@@ -18784,7 +18784,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H635" t="n">
         <v>3000</v>
@@ -18813,7 +18813,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>0.953672528266907</v>
+        <v>0.953672587871552</v>
       </c>
       <c r="H636" t="n">
         <v>17500</v>
@@ -18842,7 +18842,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G637" t="n">
-        <v>0.989660203456879</v>
+        <v>0.989660322666168</v>
       </c>
       <c r="H637" t="n">
         <v>43000</v>
@@ -19451,7 +19451,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H658" t="n">
         <v>2500</v>
@@ -19509,7 +19509,7 @@
         <v>1.25</v>
       </c>
       <c r="G660" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H660" t="n">
         <v>12500</v>
@@ -19567,7 +19567,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G662" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19596,7 +19596,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H663" t="n">
         <v>5500</v>
@@ -19625,7 +19625,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H665" t="n">
         <v>27000</v>
@@ -19799,7 +19799,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G670" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19886,7 +19886,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H673" t="n">
         <v>30500</v>
@@ -19944,7 +19944,7 @@
         <v>1.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H675" t="n">
         <v>10500</v>
@@ -19973,7 +19973,7 @@
         <v>1.25</v>
       </c>
       <c r="G676" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H676" t="n">
         <v>7000</v>
@@ -20147,7 +20147,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H682" t="n">
         <v>12000</v>
@@ -20234,7 +20234,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H685" t="n">
         <v>1000</v>
@@ -20263,7 +20263,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H686" t="n">
         <v>4000</v>
@@ -20553,7 +20553,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H696" t="n">
         <v>31000</v>
@@ -20814,7 +20814,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G705" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H705" t="n">
         <v>39500</v>
@@ -20988,7 +20988,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H711" t="n">
         <v>9500</v>
@@ -21017,7 +21017,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G712" t="n">
-        <v>1.50248408317566</v>
+        <v>1.50248420238495</v>
       </c>
       <c r="H712" t="n">
         <v>18500</v>
@@ -21162,7 +21162,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G717" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H717" t="n">
         <v>3000</v>
@@ -21249,7 +21249,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G720" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H720" t="n">
         <v>25500</v>
@@ -21307,7 +21307,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G722" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H722" t="n">
         <v>13500</v>
@@ -21336,7 +21336,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H723" t="n">
         <v>8000</v>
@@ -21423,7 +21423,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G726" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H726" t="n">
         <v>1000</v>
@@ -21452,7 +21452,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G727" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H727" t="n">
         <v>16000</v>
@@ -21481,7 +21481,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H730" t="n">
         <v>3500</v>
@@ -21684,7 +21684,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G735" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H735" t="n">
         <v>14000</v>
@@ -21916,7 +21916,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G743" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H743" t="n">
         <v>14500</v>
@@ -22119,7 +22119,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G750" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H750" t="n">
         <v>32500</v>
@@ -23250,7 +23250,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G789" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H789" t="n">
         <v>32000</v>
@@ -23308,7 +23308,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G791" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H791" t="n">
         <v>1000</v>
@@ -23656,7 +23656,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G803" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H803" t="n">
         <v>18500</v>
@@ -23685,7 +23685,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G804" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H804" t="n">
         <v>5000</v>
@@ -24091,7 +24091,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G818" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H818" t="n">
         <v>10000</v>
@@ -24120,7 +24120,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G819" t="n">
-        <v>1.44850265979767</v>
+        <v>1.44850277900696</v>
       </c>
       <c r="H819" t="n">
         <v>6000</v>
@@ -24410,7 +24410,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H829" t="n">
         <v>3000</v>
@@ -24439,7 +24439,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H830" t="n">
         <v>2000</v>
@@ -24584,7 +24584,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.53847181797028</v>
+        <v>1.53847193717957</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -24758,7 +24758,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G841" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H841" t="n">
         <v>14500</v>
@@ -24845,7 +24845,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G844" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H844" t="n">
         <v>17500</v>
@@ -24903,7 +24903,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G846" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H846" t="n">
         <v>18500</v>
@@ -25077,7 +25077,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G852" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H852" t="n">
         <v>12500</v>
@@ -25309,7 +25309,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G860" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H860" t="n">
         <v>3500</v>
@@ -25338,7 +25338,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G861" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H861" t="n">
         <v>3000</v>
@@ -25367,7 +25367,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G870" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H870" t="n">
         <v>2500</v>
@@ -25628,7 +25628,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G871" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H871" t="n">
         <v>6500</v>
@@ -25657,7 +25657,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G872" t="n">
-        <v>1.43050897121429</v>
+        <v>1.430508852005</v>
       </c>
       <c r="H872" t="n">
         <v>8000</v>
@@ -25744,7 +25744,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H875" t="n">
         <v>500</v>
@@ -25773,7 +25773,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H876" t="n">
         <v>7500</v>
@@ -25802,7 +25802,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G877" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H877" t="n">
         <v>1000</v>
@@ -25831,7 +25831,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G878" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26092,7 +26092,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G887" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H887" t="n">
         <v>1000</v>
@@ -26121,7 +26121,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G888" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G889" t="n">
-        <v>1.42151200771332</v>
+        <v>1.42151212692261</v>
       </c>
       <c r="H889" t="n">
         <v>1500</v>
@@ -26759,7 +26759,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G910" t="n">
-        <v>1.17859542369843</v>
+        <v>1.17859530448914</v>
       </c>
       <c r="H910" t="n">
         <v>8000</v>
@@ -26904,7 +26904,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G915" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H915" t="n">
         <v>14000</v>
@@ -26991,7 +26991,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G918" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H918" t="n">
         <v>9500</v>
@@ -27049,7 +27049,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27107,7 +27107,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G922" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H922" t="n">
         <v>500</v>
@@ -27136,7 +27136,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H923" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G925" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H925" t="n">
         <v>3500</v>
@@ -27223,7 +27223,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G926" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G929" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H929" t="n">
         <v>22000</v>
@@ -27455,7 +27455,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G934" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H934" t="n">
         <v>8000</v>
@@ -27484,7 +27484,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G935" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H935" t="n">
         <v>5500</v>
@@ -27513,7 +27513,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G936" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>1.20108759403229</v>
+        <v>1.20108771324158</v>
       </c>
       <c r="H938" t="n">
         <v>3500</v>
@@ -27600,7 +27600,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>1.20108759403229</v>
+        <v>1.20108771324158</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G961" t="n">
-        <v>1.29105663299561</v>
+        <v>1.2910567522049</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28325,7 +28325,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G964" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H964" t="n">
         <v>5000</v>
@@ -28557,7 +28557,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G972" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H972" t="n">
         <v>3500</v>
@@ -28644,7 +28644,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H975" t="n">
         <v>1000</v>
@@ -28673,7 +28673,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H976" t="n">
         <v>2000</v>
@@ -28702,7 +28702,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H978" t="n">
         <v>1000</v>
@@ -28818,7 +28818,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G981" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H981" t="n">
         <v>2500</v>
@@ -28963,7 +28963,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G986" t="n">
-        <v>1.17409682273865</v>
+        <v>1.17409694194794</v>
       </c>
       <c r="H986" t="n">
         <v>6500</v>
@@ -28992,7 +28992,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G987" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H987" t="n">
         <v>500</v>
@@ -29021,7 +29021,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G988" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -29050,7 +29050,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G989" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G990" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G992" t="n">
-        <v>1.19209086894989</v>
+        <v>1.1920907497406</v>
       </c>
       <c r="H992" t="n">
         <v>1000</v>
@@ -29166,7 +29166,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G993" t="n">
-        <v>1.19209086894989</v>
+        <v>1.1920907497406</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>1.19209086894989</v>
+        <v>1.1920907497406</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G997" t="n">
-        <v>1.17859542369843</v>
+        <v>1.17859530448914</v>
       </c>
       <c r="H997" t="n">
         <v>500</v>
@@ -29340,7 +29340,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G999" t="n">
-        <v>1.12011539936066</v>
+        <v>1.12011551856995</v>
       </c>
       <c r="H999" t="n">
         <v>4500</v>
@@ -29514,7 +29514,7 @@
         <v>1.25</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1005" t="n">
         <v>1500</v>
@@ -29543,7 +29543,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1006" t="n">
         <v>9000</v>
@@ -29601,7 +29601,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29630,7 +29630,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1009" t="n">
         <v>9500</v>
@@ -29659,7 +29659,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1011" t="n">
         <v>2500</v>
@@ -29717,7 +29717,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -29775,7 +29775,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.14260768890381</v>
+        <v>1.1426078081131</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>1.25</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1022" t="n">
         <v>4000</v>
@@ -30036,7 +30036,7 @@
         <v>1.25</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1023" t="n">
         <v>1500</v>
@@ -30065,7 +30065,7 @@
         <v>1.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1031" t="n">
         <v>11500</v>
@@ -30297,7 +30297,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -30326,7 +30326,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10662007331848</v>
+        <v>1.10662019252777</v>
       </c>
       <c r="H1033" t="n">
         <v>3000</v>
@@ -30384,7 +30384,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.12011539936066</v>
+        <v>1.12011551856995</v>
       </c>
       <c r="H1035" t="n">
         <v>500</v>
@@ -30442,7 +30442,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H1037" t="n">
         <v>3000</v>
@@ -30558,7 +30558,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1041" t="n">
         <v>7500</v>
@@ -30674,7 +30674,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1045" t="n">
         <v>1000</v>
@@ -30703,7 +30703,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1052" t="n">
         <v>2000</v>
@@ -30993,7 +30993,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H1056" t="n">
         <v>6000</v>
@@ -31080,7 +31080,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1059" t="n">
         <v>500</v>
@@ -31109,7 +31109,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1060" t="n">
         <v>2500</v>
@@ -31138,7 +31138,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31167,7 +31167,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31196,7 +31196,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.917684972286224</v>
+        <v>0.91768491268158</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1064" t="n">
         <v>4000</v>
@@ -31254,7 +31254,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.926681816577911</v>
+        <v>0.926681876182556</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -31283,7 +31283,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1066" t="n">
         <v>500</v>
@@ -31312,7 +31312,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -31341,7 +31341,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -31399,7 +31399,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.949174106121063</v>
+        <v>0.949174046516418</v>
       </c>
       <c r="H1070" t="n">
         <v>7500</v>
@@ -31457,7 +31457,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1072" t="n">
         <v>4000</v>
@@ -31486,7 +31486,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.980663418769836</v>
+        <v>0.980663359165192</v>
       </c>
       <c r="H1073" t="n">
         <v>500</v>
@@ -31544,7 +31544,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1075" t="n">
         <v>1500</v>
@@ -31573,7 +31573,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1076" t="n">
         <v>500</v>
@@ -31602,7 +31602,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.935678780078888</v>
+        <v>0.935678720474243</v>
       </c>
       <c r="H1077" t="n">
         <v>13500</v>
@@ -31776,7 +31776,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1083" t="n">
         <v>1000</v>
@@ -31805,7 +31805,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31834,7 +31834,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1085" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1086" t="n">
         <v>0</v>
@@ -31892,7 +31892,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1087" t="n">
         <v>0</v>
@@ -31921,7 +31921,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.998657166957855</v>
+        <v>0.99865710735321</v>
       </c>
       <c r="H1088" t="n">
         <v>3500</v>
@@ -32008,7 +32008,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1091" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>1.25</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1092" t="n">
         <v>1000</v>
@@ -32791,7 +32791,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H1118" t="n">
         <v>2000</v>
@@ -32936,7 +32936,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1123" t="n">
         <v>6500</v>
@@ -32965,7 +32965,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1124" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.07063245773315</v>
+        <v>1.07063257694244</v>
       </c>
       <c r="H1136" t="n">
         <v>2500</v>
@@ -33342,7 +33342,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1137" t="n">
         <v>2500</v>
@@ -33371,7 +33371,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1138" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1139" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.05713713169098</v>
+        <v>1.05713701248169</v>
       </c>
       <c r="H1140" t="n">
         <v>0</v>
@@ -33487,7 +33487,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.03014624118805</v>
+        <v>1.03014636039734</v>
       </c>
       <c r="H1143" t="n">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.01665091514587</v>
+        <v>1.01665103435516</v>
       </c>
       <c r="H1145" t="n">
         <v>8000</v>
@@ -33719,7 +33719,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.11561703681946</v>
+        <v>1.11561691761017</v>
       </c>
       <c r="H1150" t="n">
         <v>8000</v>
@@ -33777,7 +33777,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H1152" t="n">
         <v>19500</v>
@@ -33835,7 +33835,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.21008455753326</v>
+        <v>1.21008467674255</v>
       </c>
       <c r="H1154" t="n">
         <v>6500</v>
@@ -33864,7 +33864,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H1155" t="n">
         <v>10500</v>
@@ -34067,7 +34067,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1162" t="n">
         <v>23000</v>
@@ -34096,7 +34096,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1163" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1164" t="n">
         <v>2500</v>
@@ -34183,7 +34183,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H1166" t="n">
         <v>17000</v>
@@ -34386,7 +34386,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.22357988357544</v>
+        <v>1.22358000278473</v>
       </c>
       <c r="H1173" t="n">
         <v>5500</v>
@@ -34415,7 +34415,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1174" t="n">
         <v>5500</v>
@@ -34444,7 +34444,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1176" t="n">
         <v>500</v>
@@ -34589,7 +34589,7 @@
         <v>1.25</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.12461400032043</v>
+        <v>1.12461388111115</v>
       </c>
       <c r="H1180" t="n">
         <v>19500</v>
@@ -34647,7 +34647,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1182" t="n">
         <v>10000</v>
@@ -34676,7 +34676,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.10212171077728</v>
+        <v>1.10212159156799</v>
       </c>
       <c r="H1183" t="n">
         <v>45500</v>
@@ -34763,7 +34763,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.25506913661957</v>
+        <v>1.25506901741028</v>
       </c>
       <c r="H1186" t="n">
         <v>52000</v>
@@ -34821,7 +34821,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.18759226799011</v>
+        <v>1.1875923871994</v>
       </c>
       <c r="H1188" t="n">
         <v>1000</v>
@@ -34850,7 +34850,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.20558619499207</v>
+        <v>1.20558607578278</v>
       </c>
       <c r="H1189" t="n">
         <v>53000</v>
@@ -35024,7 +35024,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H1195" t="n">
         <v>5000</v>
@@ -35053,7 +35053,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.24157381057739</v>
+        <v>1.2415736913681</v>
       </c>
       <c r="H1196" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1197" t="n">
         <v>76000</v>
@@ -35111,7 +35111,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.43950593471527</v>
+        <v>1.43950581550598</v>
       </c>
       <c r="H1198" t="n">
         <v>85500</v>
@@ -35256,7 +35256,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1203" t="n">
         <v>8500</v>
@@ -35285,7 +35285,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.35853350162506</v>
+        <v>1.35853362083435</v>
       </c>
       <c r="H1204" t="n">
         <v>0</v>
